--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT13"/>
+  <dimension ref="A1:BT47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2738,6 +2738,6006 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Allie Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612))</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>$228.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>7866357162</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001908612</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Arrowroot Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Arrowroot Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0002017744))</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4553 GLENCOE AVENUE, SUITE 200, MARINA DEL REY, CA, 90292</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>$302.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002017744</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>Arrowroot Family Office, LLC's iShares U.S. Treasury Bond ETF(GOVT) Holding History - GuruFocus</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdzloS3pOS1RwMFRYMmotX1lOSHQwXzlialdKR0t6UG05VDNfVldMR21KZWdBV0pCUEV4eEp4cjdJYzdjQXBIWmhEcG9MZk5wY1hOLWMyTF9zOE5QM0IyMXg3LTdKaVlZeDE1SU1ONlhQY2MydEZzVG14c1piQk5tcW00SVdYZkk?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aurelius Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Aurelius Family Office Llc' (SEC 13F-HR 2026-07-13 (CIK 0002053738))</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3 EXECUTIVE PARK DR, SUITE 261, BEDFORD, NH, 03110</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>$253.9M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>6036028550</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002053738</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Biltmore Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Biltmore Family Office, Llc' (SEC 13F-HR 2026-05-11 (CIK 0001731123))</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>500 EAST BOULEVARD, CHARLOTTE, NC, 28203</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>$715.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>President/Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>704-272-4698</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001731123</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Boston Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807))</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>20 CUSTOM HOUSE STREET, SUITE 700, BOSTON, MA, 02110</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>$1.50B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>6176240800</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001039807</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Callan Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Callan Family Office, Llc' (SEC 13F-HR 2026-05-13 (CIK 0001938970))</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>201 KING OF PRUSSIA ROAD, SUITE 650, RADNOR, PA, 19087</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>$4.41B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>CEO and CCO</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>(267) 250-2036</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001938970</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cambient Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Cambient Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002105684))</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4690 FULTON STREET E, SUITE 203, ADA, MI, 49301</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>$716.4M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Trust Advisor, Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>(616) 330-2270</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002105684</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capitol Family Office, Inc.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768))</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1500 NW BETHANY BLVD., SUITE 200, BEAVERTON, OR, 97006</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>25</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>$84.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>503-897-0236</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001863768</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Collective Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Collective Family Office Llc' (SEC 13F-HR 2026-07-02 (CIK 0001845066))</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>235 ST. CHARLES WAY, STE. 200, YORK, PA, 17402</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>25</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>$489.1M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>CCO/COO</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>717-893-5055</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001845066</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colony Family Offices, Llc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Colony Family Offices, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001633573))</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4250 CONGRESS STREET, SUITE 175, CHARLOTTE, NC, 28209</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>$455.1M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Managing Director/Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>704-285-7300</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001633573</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Covenant Multifamily Offices, Llc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>firm's own name states multi-family: 'Covenant Multifamily Offices, Llc'</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>18756 STONE OAK PARKWAY, SUITE 102, SAN ANTONIO, TX, 78258</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>$556.9M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>210-403-5350</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001599749</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Custos Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Custos Family Office, Llc' (SEC 13F-HR 2026-02-17 (CIK 0001904423))</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>9011 MOUNTAIN RIDGE DRIVE, SUITE 200, AUSTIN, TX, 78759</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>$146.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>3035787024</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001904423</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cva Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084))</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>255 FILLMORE STREET, SUITE 500, DENVER, CO, 80206</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>$949.65B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Dir of Wealth Advisory</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>3032435611</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001802084</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fiduciary Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280))</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Fri, 21 Nov 2025</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>$350.8M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>(561) 353-4440</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002020280</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>Fiduciary Family Office, LLC - bocaratonobserver.com</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5hMDdCbHRNSXhyNENZbmZNbWJxTGEtMjdOWTY3M3VVaThfMXdtRVBUeTZpaWZEMFdBLU9wbENsN3BHRnhkQXRUOUxKeFF5TmZsY2VPTXM2MXJiYkxqLTZrZnFETnVLTVVnYnh1VUFub0dMTHRYbUHSAYABQVVfeXFMUGhUTnRRSnk3T2c4YWM0eGUyQnowS2R6cEI0SjZpMGFXd3VVZ0RqdklEZFhacEtLYjRnV0ZPam9mVmwzN0FCUWlydTVkS0Q0S0N5b1VjaEpzOUgzUHV2UzNSNzRwYTRQRGE2M202ZlNuN2RrY3Nkc3ptWkIxc055S2s?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>Fri, 21 Nov 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fortitude Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Fortitude Family Office, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001950506))</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7500 N DOBSON RD, SUITE 151, SCOTTSDALE, AZ, 85256</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>$516.00B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>602-834-0089</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001950506</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>Fortitude Family Office, LLC's Avantis Total Equity Markets(AVTM) Holding History - GuruFocus</t>
+        </is>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTlZLRUVod3Z0ZzJ0VjM5Z0xIOE5iM3pKNnVVMGlxdjdjWkM1QzExOGxpLVVJb3RGQnRuYjBPMVc2WTEta21SQ2JXMDRlbEtTVGFnVjdtc2V1V0t3eWkyOUNIaGw5ZlNBanRwVjZzaG9TTjlzU08zanhQcE52M19VRHM3OXBqU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Geller Family Office Services, Llc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Geller Family Office Services, Llc' (SEC 13F-HR 2025-02-14 (CIK 0001354739))</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>909 THIRD AVENUE, 16TH FLOOR, ATTN: CHIEF COMPLIANCE OFFICER, NEW YORK, NY, 10022</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>25</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>$1.52B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>212-583-6000</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001354739</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN29" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Genspring Family Offices Llc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>150 SOUTH U.S. HIGHWAY 1, JUPITER, FL, 33477</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Wed, 17 Oct 2012</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>561-354-2551</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001318447</t>
+        </is>
+      </c>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN30" t="inlineStr">
+        <is>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="BO30" t="inlineStr">
+        <is>
+          <t>How being a $19-billion family office roll-up owned by a bank finally caught up with GenSpring - RIABiz</t>
+        </is>
+      </c>
+      <c r="BP30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNS015ZDRPX2tnY3ZMbXJQa0JFbndlai1ZellqYndvR0pRVmQ2YnFxbzRSWGQ1MEg4UTVDNjE2d1U0UnVROHRpYzctMDBEU2J2aFlnSkFlZE11ZllwMzE4bi1DazlHZ1JvdkhoOTBiR2N4RFZlRUFyaE91b1l3M3E4TFJJNnlzVFJYU1NfN05xZ2ZhMWk1S1N2dDdBLWs5UFk0ZmcxWWY4M1hOM2FEYko0d2xTZmstYUhoWFJsckhIVWJFUVk?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT30" t="inlineStr">
+        <is>
+          <t>Wed, 17 Oct 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Heritage Family Offices, Llp</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Heritage Family Offices, Llp' (SEC 13F-HR 2026-04-08 (CIK 0002019316))</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>9841 E BELL RD,, STE 110, SCOTTSDALE, AZ, 85260</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>$225.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>602-775-5400</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002019316</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Independent Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Independent Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0001756485))</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>677 BROADWAY, 7TH FLOOR, ALBANY, NY, 12207</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>$243.0M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>(518) 452-8050</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001756485</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intrepid Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197))</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>25</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>$123.6M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>(203) 862-3372</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001596197</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN33" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Louis-Dreyfus Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527))</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10 WESTPORT ROAD, STE C-201, PO BOX 690, WILTON, CT, 06897</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>25</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>$64.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>203-762-6135</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001889527</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN34" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Marcuard Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112))</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>$46.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>Managing Partner &amp;amp; Assistant Vice President</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>41 43 344 60 00</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001538112</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM35" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN35" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Oneascent Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812))</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>25</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>$143.16B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>Counsel</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>2053139142</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002055812</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Pioneer Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110))</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3323 NE 163RD STREET, SUITE 604, NORTH MIAMI BEACH, FL, 33160</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>25</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>$155.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>COUNSEL</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>305-935-5502</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002135110</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pmg Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Pmg Family Office Llc' (SEC 13F-HR 2026-07-16 (CIK 0002102299))</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://pmg.proxmox.com</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5700 W PLANO PARKWAY, SUITE 2600, PLANO, TX, 75093</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sun, 22 Mar 2026</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>$108.50B (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Proxmox Mail Gateway Main Page From Proxmox Mail Gateway Jump to navigation Jump to search Proxmox Mail Gateway Statistics Proxmox Mail Gateway is an open-source email security platform based on Debian GNU/Linux. It protects your mail server from spam, viruses, trojans and phishing emails. The full featured mail proxy is deployed between the firewall and the internal mail server and allows to cont</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>https://pmg.proxmox.com</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>2145508790</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002102299</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="BO38" t="inlineStr">
+        <is>
+          <t>PMG Family Office buys 3,064 Apple shares worth $780K amid positive analyst outlooks. - Pluang</t>
+        </is>
+      </c>
+      <c r="BP38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5GbC0zREhIb1hfU2FLX0hFbV9UR0V5ZHdhbGZ0cmJHejR4dHY4V2lkWS1wdFZXdDNsalFxOHJPZzZGS0p3ajR5alh1ME5ka1hfOFFZalJoWmhUbXN4Q21XRGlLSkhyLTRWd09uWXZnd29SU1Z1dzFaMDV3?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ38" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS38" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT38" t="inlineStr">
+        <is>
+          <t>Sun, 22 Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Riverglades Family Offices Llc</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779))</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>25</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>$170.1M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>2392634079</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001619779</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM39" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN39" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="BO39" t="inlineStr"/>
+      <c r="BP39" t="inlineStr"/>
+      <c r="BQ39" t="inlineStr"/>
+      <c r="BR39" t="inlineStr"/>
+      <c r="BS39" t="inlineStr"/>
+      <c r="BT39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Standard Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494))</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>$96.8M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>6054967760</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001809494</t>
+        </is>
+      </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM40" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="BO40" t="inlineStr"/>
+      <c r="BP40" t="inlineStr"/>
+      <c r="BQ40" t="inlineStr"/>
+      <c r="BR40" t="inlineStr"/>
+      <c r="BS40" t="inlineStr"/>
+      <c r="BT40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Stenger Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106))</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>50</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>$629.4M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>Vice President, Operations</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>630-912-8295</t>
+        </is>
+      </c>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002056106</t>
+        </is>
+      </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM41" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="BO41" t="inlineStr">
+        <is>
+          <t>Stenger Family Office LLC Has $28.84 Million Holdings in Microsoft Corporation $MSFT - MarketBeat</t>
+        </is>
+      </c>
+      <c r="BP41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcEd4UEw5VkZiVEt5a1lCQnl5NTdxNFVWUDVad0N4ODFySUtCZUFOcnhaSHhLN2lodVA2T1BGQnN5RlZOWXFoYnpDdVY1bkd0bGZ5c25jaW01Mk96NnVzN2hkMVB0Q3UxMEhBdUtZMjBNU1BPS3p1aENKQUJxSUdtYklGQVFQcGQ0TjdhUmYtYzU3cURLZzBrc0pvZ0tGMXhqZm94cGlHS1BTbWc4eVd3YkhVYzNkLTlhYlBnV2FDQXhDd0pwVFpZV0I4bWItVlNFNGFPNjlxR1BMQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ41" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS41" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT41" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Stokes Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278))</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>25</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>$969.0M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>5043994100</t>
+        </is>
+      </c>
+      <c r="BJ42" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001802278</t>
+        </is>
+      </c>
+      <c r="BK42" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM42" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="BO42" t="inlineStr"/>
+      <c r="BP42" t="inlineStr"/>
+      <c r="BQ42" t="inlineStr"/>
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="inlineStr"/>
+      <c r="BT42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tarbox Family Office, Inc.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603))</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>25</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>$615.8M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>949-721-2330</t>
+        </is>
+      </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001599603</t>
+        </is>
+      </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM43" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN43" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="BO43" t="inlineStr"/>
+      <c r="BP43" t="inlineStr"/>
+      <c r="BQ43" t="inlineStr"/>
+      <c r="BR43" t="inlineStr"/>
+      <c r="BS43" t="inlineStr"/>
+      <c r="BT43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Timonier Family Office, Ltd.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170))</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>$315.1M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>Chief Compliance Office</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>3367255010</t>
+        </is>
+      </c>
+      <c r="BJ44" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002038170</t>
+        </is>
+      </c>
+      <c r="BK44" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="BO44" t="inlineStr"/>
+      <c r="BP44" t="inlineStr"/>
+      <c r="BQ44" t="inlineStr"/>
+      <c r="BR44" t="inlineStr"/>
+      <c r="BS44" t="inlineStr"/>
+      <c r="BT44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Virtus Family Office Llc</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482))</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>25</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>$117.2M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>9157303885</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001913482</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="BO45" t="inlineStr"/>
+      <c r="BP45" t="inlineStr"/>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr"/>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Waveland Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>570 LAKE COOK RD, SUITE 320, DEERFIELD, IL, 60015</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tue, 04 Feb 2025</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>50</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>312-961-7612</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002007105</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN46" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="BO46" t="inlineStr">
+        <is>
+          <t>CLEARSTEAD ADVISORS ANNOUNCES ACQUISITION OF WAVELAND FAMILY OFFICE - PR Newswire</t>
+        </is>
+      </c>
+      <c r="BP46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQX0MtMV9XT1JNRjFfdlpwc3p1MEg4ZTJ4a050ZDFTQ2gzWEVOc25TaVAwaEFOWE02aXdid3g4QjUwN1lYRGt4ajE1aDBVYy1kWHkwMng0WUVVMUVTd2dtNlZFeS15M3F1M09ndmF5RVI0SmUxUmpQdnozQ2tVem1HOTRQaGR4UG1XcVYteTFQSm1xVVlPUnhCRlFxYVFsUE1uRWRocFdITy0xcFpUWVpYYlJFZUxhSV9tT09DczBsUUg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT46" t="inlineStr">
+        <is>
+          <t>Tue, 04 Feb 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, Llc</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SEC CIK registry (entity names)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441))</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>25</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Qualified</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>$35.9M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>303-968-1737</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001835441</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN47" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr"/>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -923,7 +923,11 @@
           <t>SEC-registered operating entity (CIK 0001878856) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://longboatfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>500 MAMARONECK AVENUE, SUITE 213, HARRISON, NY, 10528</t>
@@ -1039,12 +1043,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Duquesne Family Office LLC' (SEC 13F-HR 2026-05-15 (CIK 0001536411))</t>
+          <t>files SEC 13F-HR as 'Duquesne Family Office LLC' (SEC 13F-HR 2026-05-15 (CIK 0001536411)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1243,12 +1247,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689))</t>
+          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1423,7 +1427,11 @@
           <t>SFO evidence in gathered text: ['one family']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://pathstone.com</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>10 STERLING BLVD, SUITE 402, ENGLEWOOD, NJ, 07631</t>
@@ -1931,7 +1939,11 @@
           <t>SEC-registered operating entity (CIK 0001542604) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://pinnacleinvestment.com</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>5910 NORTH CENTRAL EXPRESSWAY, SUITE 1475, DALLAS, TX, 75206</t>
@@ -3351,15 +3363,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612))</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://allie-intl.com</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
@@ -3369,7 +3385,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3467,12 +3483,36 @@
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>info@allie-intl.com</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>https://allie-intl.com</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>7866357162</t>
@@ -3531,7 +3571,11 @@
           <t>SEC-registered operating entity (CIK 0001930338) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://antillesfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>5330 YACHT HAVEN GRANDE, SUITE 206, ST THOMAS, VI, 00802</t>
@@ -3647,15 +3691,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Arrowroot Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0002017744))</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Arrowroot Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0002017744)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://arrowrootfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>4553 GLENCOE AVENUE, SUITE 200, MARINA DEL REY, CA, 90292</t>
@@ -3851,15 +3899,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Aurelius Family Office Llc' (SEC 13F-HR 2026-07-13 (CIK 0002053738))</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Aurelius Family Office Llc' (SEC 13F-HR 2026-07-13 (CIK 0002053738)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://aurelius.net</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>3 EXECUTIVE PARK DR, SUITE 261, BEDFORD, NH, 03110</t>
@@ -3869,7 +3921,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3967,12 +4019,36 @@
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>info@aurelius.net</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>https://aurelius.net</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI22" t="inlineStr">
         <is>
           <t>6036028550</t>
@@ -4147,15 +4223,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Biltmore Family Office, Llc' (SEC 13F-HR 2026-05-11 (CIK 0001731123))</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Biltmore Family Office, Llc' (SEC 13F-HR 2026-05-11 (CIK 0001731123)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://biltmorefamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>500 EAST BOULEVARD, CHARLOTTE, NC, 28203</t>
@@ -4447,12 +4527,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807))</t>
+          <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -4619,15 +4699,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Callan Family Office, Llc' (SEC 13F-HR 2026-05-13 (CIK 0001938970))</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Callan Family Office, Llc' (SEC 13F-HR 2026-05-13 (CIK 0001938970)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>201 KING OF PRUSSIA ROAD, SUITE 650, RADNOR, PA, 19087</t>
@@ -4791,15 +4875,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Cambient Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002105684))</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Cambient Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002105684)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://cambient.com</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>4690 FULTON STREET E, SUITE 203, ADA, MI, 49301</t>
@@ -4809,7 +4897,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4907,12 +4995,36 @@
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
-      <c r="BF28" t="inlineStr"/>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>info@cambient.com</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>https://cambient.com</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI28" t="inlineStr">
         <is>
           <t>(616) 330-2270</t>
@@ -4963,12 +5075,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768))</t>
+          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -5135,15 +5247,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Collective Family Office Llc' (SEC 13F-HR 2026-07-02 (CIK 0001845066))</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Collective Family Office Llc' (SEC 13F-HR 2026-07-02 (CIK 0001845066)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://collectivefamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>235 ST. CHARLES WAY, STE. 200, YORK, PA, 17402</t>
@@ -5307,15 +5423,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Colony Family Offices, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001633573))</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Colony Family Offices, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001633573)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://colonyfamilyoffices.com</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>4250 CONGRESS STREET, SUITE 175, CHARLOTTE, NC, 28209</t>
@@ -5651,15 +5771,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Custos Family Office, Llc' (SEC 13F-HR 2026-02-17 (CIK 0001904423))</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Custos Family Office, Llc' (SEC 13F-HR 2026-02-17 (CIK 0001904423)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://custosfo.com</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>9011 MOUNTAIN RIDGE DRIVE, SUITE 200, AUSTIN, TX, 78759</t>
@@ -5823,12 +5947,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084))</t>
+          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -6003,7 +6127,11 @@
           <t>SEC-registered operating entity (CIK 0001559152) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://danis.com</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>112 WAMPHASSUC RD, STONINGTON, CT, 06378</t>
@@ -6127,7 +6255,11 @@
           <t>bank/wirehouse-affiliated SEC-registered family office (CIK 0001759113, verified filing address/phone)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://deutsche-oppenheim.de</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>11 OPPENHEIM STREET, COLOGNE, 2M, 50668</t>
@@ -6145,7 +6277,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -6195,12 +6327,36 @@
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
-      <c r="BG36" t="inlineStr"/>
-      <c r="BH36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>info@deutsche-oppenheim.de</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>https://deutsche-oppenheim.de</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI36" t="inlineStr">
         <is>
           <t>49221577720</t>
@@ -6407,15 +6563,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280))</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://fiduciaryfo.com</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
@@ -6433,7 +6593,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -6531,12 +6691,36 @@
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="inlineStr"/>
-      <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>admin@fiduciaryfo.com</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>https://fiduciaryfo.com</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI38" t="inlineStr">
         <is>
           <t>(561) 353-4440</t>
@@ -6611,15 +6795,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Fortitude Family Office, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001950506))</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Fortitude Family Office, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001950506)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://fortitudefo.com</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>7500 N DOBSON RD, SUITE 151, SCOTTSDALE, AZ, 85256</t>
@@ -6815,15 +7003,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Geller Family Office Services, Llc' (SEC 13F-HR 2025-02-14 (CIK 0001354739))</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Geller Family Office Services, Llc' (SEC 13F-HR 2025-02-14 (CIK 0001354739)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://gellerco.com</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>909 THIRD AVENUE, 16TH FLOOR, ATTN: CHIEF COMPLIANCE OFFICER, NEW YORK, NY, 10022</t>
@@ -7143,15 +7335,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Heritage Family Offices, Llp' (SEC 13F-HR 2026-04-08 (CIK 0002019316))</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Heritage Family Offices, Llp' (SEC 13F-HR 2026-04-08 (CIK 0002019316)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://heritagefo.com</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>9841 E BELL RD,, STE 110, SCOTTSDALE, AZ, 85260</t>
@@ -7315,15 +7511,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Independent Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0001756485))</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Independent Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0001756485)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://ifollc.com</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>677 BROADWAY, 7TH FLOOR, ALBANY, NY, 12207</t>
@@ -7333,7 +7533,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -7431,12 +7631,36 @@
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="inlineStr"/>
       <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
-      <c r="BD43" t="inlineStr"/>
-      <c r="BE43" t="inlineStr"/>
-      <c r="BF43" t="inlineStr"/>
-      <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>dr@ifollc.com</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>https://ifollc.com</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI43" t="inlineStr">
         <is>
           <t>(518) 452-8050</t>
@@ -7487,15 +7711,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197))</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://intrepidtravel.com</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
@@ -7791,7 +8019,11 @@
           <t>SEC-registered operating entity (CIK 0001551648) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://lex-life.com</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>9005 OVERLOOK BLVD., BRENTWOOD, TN, 37027</t>
@@ -7801,7 +8033,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -7851,12 +8083,36 @@
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
-      <c r="BC46" t="inlineStr"/>
-      <c r="BD46" t="inlineStr"/>
-      <c r="BE46" t="inlineStr"/>
-      <c r="BF46" t="inlineStr"/>
-      <c r="BG46" t="inlineStr"/>
-      <c r="BH46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>team@lex-life.com</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>https://lex-life.com</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI46" t="inlineStr">
         <is>
           <t>386-566-7249</t>
@@ -7915,7 +8171,11 @@
           <t>SEC-registered operating entity (CIK 0002014891) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://looper.com</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>2000 BERING DR SUITE 875, HOUSTON, TX, 77057</t>
@@ -7925,7 +8185,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -7975,12 +8235,36 @@
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="inlineStr"/>
-      <c r="BE47" t="inlineStr"/>
-      <c r="BF47" t="inlineStr"/>
-      <c r="BG47" t="inlineStr"/>
-      <c r="BH47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>staff@looper.com</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>https://looper.com</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI47" t="inlineStr">
         <is>
           <t>2142262606</t>
@@ -8031,12 +8315,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527))</t>
+          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -8203,15 +8487,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112))</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://marcuardfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
@@ -8375,15 +8663,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812))</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://oneascent.com</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
@@ -8547,12 +8839,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110))</t>
+          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -8719,12 +9011,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Pmg Family Office Llc' (SEC 13F-HR 2026-07-16 (CIK 0002102299))</t>
+          <t>files SEC 13F-HR as 'Pmg Family Office Llc' (SEC 13F-HR 2026-07-16 (CIK 0002102299)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -8951,7 +9243,11 @@
           <t>SEC-registered operating entity (CIK 0002102280) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://p1fo.com</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>919 MANHATTAN AVENUE, SUITE 101, MANHATTAN BEACH, CA, 90266</t>
@@ -8961,7 +9257,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -9011,12 +9307,36 @@
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="inlineStr"/>
       <c r="BB53" t="inlineStr"/>
-      <c r="BC53" t="inlineStr"/>
-      <c r="BD53" t="inlineStr"/>
-      <c r="BE53" t="inlineStr"/>
-      <c r="BF53" t="inlineStr"/>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>info@p1fo.com</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>https://p1fo.com</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
           <t>8183973514</t>
@@ -9075,7 +9395,11 @@
           <t>SEC-registered operating entity (CIK 0001735765) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://qvt.com</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>INTERTRUST CORPORATE SERVICES (CAYMAN), LTD., 190 ELGIN AVENUE, GEORGE TOWN, GRAND CAYMAN, E9, KY1-9005</t>
@@ -9085,7 +9409,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -9135,12 +9459,36 @@
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
-      <c r="BC54" t="inlineStr"/>
-      <c r="BD54" t="inlineStr"/>
-      <c r="BE54" t="inlineStr"/>
-      <c r="BF54" t="inlineStr"/>
-      <c r="BG54" t="inlineStr"/>
-      <c r="BH54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>reception@qvt.com</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>https://qvt.com</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI54" t="inlineStr">
         <is>
           <t>345-943-3100</t>
@@ -9199,7 +9547,11 @@
           <t>SEC-registered operating entity (CIK 0001736966) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://qvt.com</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>1177 AVENUE OF THE AMERICAS, 9TH FLOOR, NEW YORK, NY, 10036</t>
@@ -9209,7 +9561,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -9259,12 +9611,36 @@
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
-      <c r="BC55" t="inlineStr"/>
-      <c r="BD55" t="inlineStr"/>
-      <c r="BE55" t="inlineStr"/>
-      <c r="BF55" t="inlineStr"/>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>reception@qvt.com</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>https://qvt.com</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI55" t="inlineStr">
         <is>
           <t>212-705-8888</t>
@@ -9315,15 +9691,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779))</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://rivergladesfo.com</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
@@ -9495,7 +9875,11 @@
           <t>SEC-registered operating entity (CIK 0001185043) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://archbridge.com</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>101 S HANLEY ROAD, SUITE 1085, ST LOUIS, MO, 63105</t>
@@ -9505,7 +9889,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -9555,12 +9939,36 @@
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="inlineStr"/>
       <c r="BB57" t="inlineStr"/>
-      <c r="BC57" t="inlineStr"/>
-      <c r="BD57" t="inlineStr"/>
-      <c r="BE57" t="inlineStr"/>
-      <c r="BF57" t="inlineStr"/>
-      <c r="BG57" t="inlineStr"/>
-      <c r="BH57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>info@archbridge.com</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>https://archbridge.com</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI57" t="inlineStr">
         <is>
           <t>3147274600</t>
@@ -9611,15 +10019,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494))</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://standardsolomon.com</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
@@ -9783,15 +10195,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106))</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
@@ -9809,7 +10225,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -9907,12 +10323,36 @@
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="inlineStr"/>
       <c r="BB59" t="inlineStr"/>
-      <c r="BC59" t="inlineStr"/>
-      <c r="BD59" t="inlineStr"/>
-      <c r="BE59" t="inlineStr"/>
-      <c r="BF59" t="inlineStr"/>
-      <c r="BG59" t="inlineStr"/>
-      <c r="BH59" t="inlineStr"/>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>https://stengerfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="BE59" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI59" t="inlineStr">
         <is>
           <t>630-912-8295</t>
@@ -9987,15 +10427,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278))</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://stokesfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
@@ -10159,15 +10603,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603))</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://tarbox.com</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
@@ -10331,15 +10779,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170))</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://timonier.com</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
@@ -10627,15 +11079,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482))</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://virtus-fo.com</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
@@ -10807,7 +11263,11 @@
           <t>SEC-registered operating entity (CIK 0002007105) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://wavelandgroup.com</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>570 LAKE COOK RD, SUITE 320, DEERFIELD, IL, 60015</t>
@@ -10825,7 +11285,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -10875,12 +11335,36 @@
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
-      <c r="BC65" t="inlineStr"/>
-      <c r="BD65" t="inlineStr"/>
-      <c r="BE65" t="inlineStr"/>
-      <c r="BF65" t="inlineStr"/>
-      <c r="BG65" t="inlineStr"/>
-      <c r="BH65" t="inlineStr"/>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>info@wavelandgroup.com</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>https://wavelandgroup.com</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI65" t="inlineStr">
         <is>
           <t>312-961-7612</t>
@@ -10955,15 +11439,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441))</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://wealthgate.de</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
@@ -11135,7 +11623,11 @@
           <t>SEC-registered operating entity (CIK 0001809107) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://wk-companies.com</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>6931 CHESHIRE LANE, SAINT LOUIS, MO, 63123</t>

--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -3371,11 +3371,7 @@
           <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://allie-intl.com</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
@@ -3385,7 +3381,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3483,36 +3479,12 @@
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>info@allie-intl.com</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>https://allie-intl.com</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
           <t>7866357162</t>
@@ -4535,7 +4507,11 @@
           <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://bosfam.com</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>20 CUSTOM HOUSE STREET, SUITE 700, BOSTON, MA, 02110</t>
@@ -6127,11 +6103,7 @@
           <t>SEC-registered operating entity (CIK 0001559152) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://danis.com</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>112 WAMPHASSUC RD, STONINGTON, CT, 06378</t>
@@ -7719,11 +7691,7 @@
           <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://intrepidtravel.com</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
@@ -8171,11 +8139,7 @@
           <t>SEC-registered operating entity (CIK 0002014891) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://looper.com</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>2000 BERING DR SUITE 875, HOUSTON, TX, 77057</t>
@@ -8185,7 +8149,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -8235,36 +8199,12 @@
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr">
-        <is>
-          <t>staff@looper.com</t>
-        </is>
-      </c>
-      <c r="BD47" t="inlineStr">
-        <is>
-          <t>https://looper.com</t>
-        </is>
-      </c>
-      <c r="BE47" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH47" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr">
         <is>
           <t>2142262606</t>
@@ -8671,11 +8611,7 @@
           <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://oneascent.com</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
@@ -9087,31 +9023,11 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>Proxmox Mail Gateway Main Page From Proxmox Mail Gateway Jump to navigation Jump to search Proxmox Mail Gateway Statistics Proxmox Mail Gateway is an open-source email security platform based on Debian GNU/Linux. It protects your mail server from spam, viruses, trojans and phishing emails. The full featured mail proxy is deployed between the firewall and the internal mail server and allows to cont</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>https://pmg.proxmox.com</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
@@ -9395,11 +9311,7 @@
           <t>SEC-registered operating entity (CIK 0001735765) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://qvt.com</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>INTERTRUST CORPORATE SERVICES (CAYMAN), LTD., 190 ELGIN AVENUE, GEORGE TOWN, GRAND CAYMAN, E9, KY1-9005</t>
@@ -9409,7 +9321,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -9459,36 +9371,12 @@
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
-      <c r="BC54" t="inlineStr">
-        <is>
-          <t>reception@qvt.com</t>
-        </is>
-      </c>
-      <c r="BD54" t="inlineStr">
-        <is>
-          <t>https://qvt.com</t>
-        </is>
-      </c>
-      <c r="BE54" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH54" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
           <t>345-943-3100</t>
@@ -9547,11 +9435,7 @@
           <t>SEC-registered operating entity (CIK 0001736966) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://qvt.com</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>1177 AVENUE OF THE AMERICAS, 9TH FLOOR, NEW YORK, NY, 10036</t>
@@ -9561,7 +9445,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -9611,36 +9495,12 @@
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
-      <c r="BC55" t="inlineStr">
-        <is>
-          <t>reception@qvt.com</t>
-        </is>
-      </c>
-      <c r="BD55" t="inlineStr">
-        <is>
-          <t>https://qvt.com</t>
-        </is>
-      </c>
-      <c r="BE55" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH55" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
           <t>212-705-8888</t>
@@ -9875,11 +9735,7 @@
           <t>SEC-registered operating entity (CIK 0001185043) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://archbridge.com</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>101 S HANLEY ROAD, SUITE 1085, ST LOUIS, MO, 63105</t>
@@ -9889,7 +9745,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -9939,36 +9795,12 @@
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="inlineStr"/>
       <c r="BB57" t="inlineStr"/>
-      <c r="BC57" t="inlineStr">
-        <is>
-          <t>info@archbridge.com</t>
-        </is>
-      </c>
-      <c r="BD57" t="inlineStr">
-        <is>
-          <t>https://archbridge.com</t>
-        </is>
-      </c>
-      <c r="BE57" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH57" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr">
         <is>
           <t>3147274600</t>
@@ -10027,11 +9859,7 @@
           <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://standardsolomon.com</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
@@ -10611,11 +10439,7 @@
           <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603)); single- vs multi-family unproven</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://tarbox.com</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
@@ -11263,11 +11087,7 @@
           <t>SEC-registered operating entity (CIK 0002007105) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://wavelandgroup.com</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>570 LAKE COOK RD, SUITE 320, DEERFIELD, IL, 60015</t>
@@ -11285,7 +11105,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -11335,36 +11155,12 @@
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
-      <c r="BC65" t="inlineStr">
-        <is>
-          <t>info@wavelandgroup.com</t>
-        </is>
-      </c>
-      <c r="BD65" t="inlineStr">
-        <is>
-          <t>https://wavelandgroup.com</t>
-        </is>
-      </c>
-      <c r="BE65" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BH65" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+      <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
+      <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr">
         <is>
           <t>312-961-7612</t>

--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -1419,12 +1419,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SFO evidence in gathered text: ['one family']</t>
+          <t>files SEC 13F-HR as 'PATHSTONE FAMILY OFFICE, LLC' (SEC 13F-HR 2024-01-16 (CIK 0001511137)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -781,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fiduciary Family Office, Llc</t>
+          <t>Stenger Family Office, Llc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -796,23 +796,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://fiduciaryfo.com</t>
+          <t>https://stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
+          <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fri, 21 Nov 2025</t>
+          <t>Wed, 22 Jul 2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -831,12 +831,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>$350.8M (13F portfolio value)</t>
+          <t>$629.4M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -877,20 +877,44 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Julia Patricia Foran</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Vice President, Operations</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -910,7 +934,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr"/>
@@ -921,12 +945,12 @@
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>admin@fiduciaryfo.com</t>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>https://fiduciaryfo.com</t>
+          <t>https://stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -951,12 +975,12 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>(561) 353-4440</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002020280</t>
+          <t>SEC EDGAR submissions CIK 0002056106</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -976,17 +1000,17 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>Fiduciary Family Office, LLC - bocaratonobserver.com</t>
+          <t>Stenger Family Office LLC Has $28.84 Million Holdings in Microsoft Corporation $MSFT - MarketBeat</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5hMDdCbHRNSXhyNENZbmZNbWJxTGEtMjdOWTY3M3VVaThfMXdtRVBUeTZpaWZEMFdBLU9wbENsN3BHRnhkQXRUOUxKeFF5TmZsY2VPTXM2MXJiYkxqLTZrZnFETnVLTVVnYnh1VUFub0dMTHRYbUHSAYABQVVfeXFMUGhUTnRRSnk3T2c4YWM0eGUyQnowS2R6cEI0SjZpMGFXd3VVZ0RqdklEZFhacEtLYjRnV0ZPam9mVmwzN0FCUWlydTVkS0Q0S0N5b1VjaEpzOUgzUHV2UzNSNzRwYTRQRGE2M202ZlNuN2RrY3Nkc3ptWkIxc055S2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcEd4UEw5VkZiVEt5a1lCQnl5NTdxNFVWUDVad0N4ODFySUtCZUFOcnhaSHhLN2lodVA2T1BGQnN5RlZOWXFoYnpDdVY1bkd0bGZ5c25jaW01Mk96NnVzN2hkMVB0Q3UxMEhBdUtZMjBNU1BPS3p1aENKQUJxSUdtYklGQVFQcGQ0TjdhUmYtYzU3cURLZzBrc0pvZ0tGMXhqZm94cGlHS1BTbWc4eVd3YkhVYzNkLTlhYlBnV2FDQXhDd0pwVFpZV0I4bWItVlNFNGFPNjlxR1BMQQ?oc=5</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1006,14 +1030,14 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>Fri, 21 Nov 2025</t>
+          <t>Wed, 22 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stenger Family Office, Llc</t>
+          <t>Fiduciary Family Office, Llc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1028,23 +1052,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://stengerfamilyoffice.com</t>
+          <t>https://fiduciaryfo.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
+          <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026</t>
+          <t>Fri, 21 Nov 2025</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1063,12 +1087,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>$629.4M (13F portfolio value)</t>
+          <t>$350.8M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1088,7 +1112,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -1117,12 +1141,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Vice President, Operations</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1142,7 +1166,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr"/>
@@ -1153,12 +1177,12 @@
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
+          <t>admin@fiduciaryfo.com</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>https://stengerfamilyoffice.com</t>
+          <t>https://fiduciaryfo.com</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1183,12 +1207,12 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>630-912-8295</t>
+          <t>(561) 353-4440</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002056106</t>
+          <t>SEC EDGAR submissions CIK 0002020280</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1208,17 +1232,17 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>Stenger Family Office LLC Has $28.84 Million Holdings in Microsoft Corporation $MSFT - MarketBeat</t>
+          <t>Fiduciary Family Office, LLC - bocaratonobserver.com</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcEd4UEw5VkZiVEt5a1lCQnl5NTdxNFVWUDVad0N4ODFySUtCZUFOcnhaSHhLN2lodVA2T1BGQnN5RlZOWXFoYnpDdVY1bkd0bGZ5c25jaW01Mk96NnVzN2hkMVB0Q3UxMEhBdUtZMjBNU1BPS3p1aENKQUJxSUdtYklGQVFQcGQ0TjdhUmYtYzU3cURLZzBrc0pvZ0tGMXhqZm94cGlHS1BTbWc4eVd3YkhVYzNkLTlhYlBnV2FDQXhDd0pwVFpZV0I4bWItVlNFNGFPNjlxR1BMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5hMDdCbHRNSXhyNENZbmZNbWJxTGEtMjdOWTY3M3VVaThfMXdtRVBUeTZpaWZEMFdBLU9wbENsN3BHRnhkQXRUOUxKeFF5TmZsY2VPTXM2MXJiYkxqLTZrZnFETnVLTVVnYnh1VUFub0dMTHRYbUHSAYABQVVfeXFMUGhUTnRRSnk3T2c4YWM0eGUyQnowS2R6cEI0SjZpMGFXd3VVZ0RqdklEZFhacEtLYjRnV0ZPam9mVmwzN0FCUWlydTVkS0Q0S0N5b1VjaEpzOUgzUHV2UzNSNzRwYTRQRGE2M202ZlNuN2RrY3Nkc3ptWkIxc055S2s?oc=5</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1238,7 +1262,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026</t>
+          <t>Fri, 21 Nov 2025</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1541,36 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Brenda Winslow</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>Chief Compliance Officer</t>
@@ -1717,12 +1765,36 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Josh Gibbs</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>Trust Advisor, Chief Compliance Officer</t>
@@ -1917,12 +1989,36 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>William Reickert</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>Chief Compliance Officer</t>
@@ -2125,12 +2221,36 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Lisandra Wilmott</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>2024-01-16</t>
+        </is>
+      </c>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>General Counsel &amp;amp; CCO</t>
@@ -2333,12 +2453,36 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Roberto Santos</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>CEO</t>
@@ -2495,7 +2639,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>$516.00B (13F portfolio value)</t>
+          <t>$516.0M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2541,12 +2685,36 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Drew Phillips</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>COO</t>
@@ -2745,12 +2913,36 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sue Meng</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ11" t="inlineStr">
         <is>
           <t>General Counsel</t>
@@ -2903,7 +3095,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>$108.50B (13F portfolio value)</t>
+          <t>$108.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -4377,12 +4569,36 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Christopher H. A. Cecil</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
       <c r="AQ21" t="inlineStr">
         <is>
           <t>President/Chief Compliance Officer</t>
@@ -4553,12 +4769,36 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>George Beal</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="AQ22" t="inlineStr">
         <is>
           <t>Managing Partner</t>
@@ -4729,12 +4969,36 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>John Ginter</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="AQ23" t="inlineStr">
         <is>
           <t>CEO and CCO</t>
@@ -4905,12 +5169,36 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Trevor N. Hoffman</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="AQ24" t="inlineStr">
         <is>
           <t>CCO/COO</t>
@@ -5081,12 +5369,36 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Eric D. Ridenour</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="AQ25" t="inlineStr">
         <is>
           <t>Managing Director/Chief Compliance Officer</t>
@@ -5257,12 +5569,36 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Mitchell Herr</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
       <c r="AQ26" t="inlineStr">
         <is>
           <t>Principal</t>
@@ -5433,12 +5769,36 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Beverly Duke</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
       <c r="AQ27" t="inlineStr">
         <is>
           <t>Chief Compliance Officer</t>
@@ -5609,12 +5969,36 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Michael Frost</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="AQ28" t="inlineStr">
         <is>
           <t>CCO</t>
@@ -5697,7 +6081,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marcuard Family Office Ltd</t>
+          <t>Riverglades Family Offices Llc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5712,17 +6096,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://marcuardfamilyoffice.com</t>
+          <t>https://rivergladesfo.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
+          <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -5739,12 +6123,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>$46.5M (13F portfolio value)</t>
+          <t>$170.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5764,7 +6148,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -5785,20 +6169,44 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>PJ Marinelli</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>Managing Partner &amp;amp; Assistant Vice President</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5818,7 +6226,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr"/>
@@ -5835,12 +6243,12 @@
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>41 43 344 60 00</t>
+          <t>2392634079</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001538112</t>
+          <t>SEC EDGAR submissions CIK 0001619779</t>
         </is>
       </c>
       <c r="BK29" t="inlineStr">
@@ -5860,7 +6268,7 @@
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr"/>
@@ -5873,7 +6281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Riverglades Family Offices Llc</t>
+          <t>Stokes Family Office, Llc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5888,17 +6296,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://rivergladesfo.com</t>
+          <t>https://stokesfamilyoffice.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
+          <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -5915,12 +6323,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>$170.1M (13F portfolio value)</t>
+          <t>$969.0M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5940,7 +6348,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -5961,20 +6369,44 @@
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Charles Tiblier</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>CCO</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5994,7 +6426,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr"/>
@@ -6011,12 +6443,12 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>2392634079</t>
+          <t>5043994100</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001619779</t>
+          <t>SEC EDGAR submissions CIK 0001802278</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
@@ -6036,7 +6468,7 @@
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr"/>
@@ -6049,7 +6481,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Stokes Family Office, Llc</t>
+          <t>Timonier Family Office, Ltd.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6064,17 +6496,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com</t>
+          <t>https://timonier.com</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
+          <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -6091,12 +6523,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>$969.0M (13F portfolio value)</t>
+          <t>$315.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -6116,7 +6548,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -6137,20 +6569,44 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Janice French</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>CCO</t>
+          <t>Chief Compliance Office</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -6170,7 +6626,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr"/>
@@ -6187,12 +6643,12 @@
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>5043994100</t>
+          <t>3367255010</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001802278</t>
+          <t>SEC EDGAR submissions CIK 0002038170</t>
         </is>
       </c>
       <c r="BK31" t="inlineStr">
@@ -6212,7 +6668,7 @@
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr"/>
@@ -6225,7 +6681,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Timonier Family Office, Ltd.</t>
+          <t>Virtus Family Office Llc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6240,17 +6696,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://timonier.com</t>
+          <t>https://virtus-fo.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
+          <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -6267,12 +6723,12 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>$315.1M (13F portfolio value)</t>
+          <t>$117.2M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6292,7 +6748,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -6313,20 +6769,44 @@
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Norma Angelica Peralta Morales</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>Chief Compliance Office</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -6346,7 +6826,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr"/>
@@ -6363,12 +6843,12 @@
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>3367255010</t>
+          <t>9157303885</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002038170</t>
+          <t>SEC EDGAR submissions CIK 0001913482</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
@@ -6388,7 +6868,7 @@
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr"/>
@@ -6401,7 +6881,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Virtus Family Office Llc</t>
+          <t>Wealthgate Family Office, Llc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6416,17 +6896,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://virtus-fo.com</t>
+          <t>https://wealthgate.de</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
+          <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -6443,12 +6923,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>$117.2M (13F portfolio value)</t>
+          <t>$35.9M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6468,7 +6948,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -6489,12 +6969,36 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Galen Moore</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
       <c r="AQ33" t="inlineStr">
         <is>
           <t>Chief Compliance Officer</t>
@@ -6502,7 +7006,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -6522,7 +7026,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr"/>
@@ -6539,12 +7043,12 @@
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>9157303885</t>
+          <t>303-968-1737</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001913482</t>
+          <t>SEC EDGAR submissions CIK 0001835441</t>
         </is>
       </c>
       <c r="BK33" t="inlineStr">
@@ -6564,7 +7068,7 @@
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr"/>
@@ -6577,12 +7081,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, Llc</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>SEC EDGAR full-text search</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6592,17 +7096,13 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://wealthgate.de</t>
-        </is>
-      </c>
+          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
+          <t>701 CARLSON PARKWAY, SUITE 1030, MINNETONKA, MN, 55305</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -6619,12 +7119,12 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>$35.9M (13F portfolio value)</t>
+          <t>$163.2M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6644,7 +7144,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -6665,20 +7165,44 @@
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>John P. Flakne</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -6698,7 +7222,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr"/>
@@ -6715,12 +7239,12 @@
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>303-968-1737</t>
+          <t>952-841-0400</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001835441</t>
+          <t>SEC EDGAR submissions CIK 0001683689</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
@@ -6740,7 +7264,7 @@
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr"/>
@@ -6753,12 +7277,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Allie Family Office Llc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6768,13 +7292,13 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>701 CARLSON PARKWAY, SUITE 1030, MINNETONKA, MN, 55305</t>
+          <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -6791,12 +7315,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>$163.2M (13F portfolio value)</t>
+          <t>$228.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6816,7 +7340,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -6837,20 +7361,44 @@
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Daniel Bejarano</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6870,7 +7418,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr"/>
@@ -6887,12 +7435,12 @@
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>952-841-0400</t>
+          <t>7866357162</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001683689</t>
+          <t>SEC EDGAR submissions CIK 0001908612</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
@@ -6912,7 +7460,7 @@
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr"/>
@@ -6925,12 +7473,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UBS Family Office</t>
+          <t>Capitol Family Office, Inc.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6940,15 +7488,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1500 NW BETHANY BLVD., SUITE 200, BEAVERTON, OR, 97006</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -6961,37 +7509,41 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>$84.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
@@ -6999,44 +7551,72 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Erica Nortman</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
       <c r="AY36" t="inlineStr"/>
@@ -7049,70 +7629,70 @@
       <c r="BF36" t="inlineStr"/>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
-      <c r="BI36" t="inlineStr"/>
-      <c r="BJ36" t="inlineStr"/>
-      <c r="BK36" t="inlineStr"/>
-      <c r="BL36" t="inlineStr"/>
-      <c r="BM36" t="inlineStr"/>
-      <c r="BN36" t="inlineStr"/>
-      <c r="BO36" t="inlineStr">
-        <is>
-          <t>UBS Family Office Report Highlights Strong US Exposure, AI Investment - Family Wealth Report</t>
-        </is>
-      </c>
-      <c r="BP36" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWUF1RHNZRmdaSm5HanF5d3M5QWNja2NaVmNnN3RMcE85NVZxWnJnTlpTdkU5ODVWWlQxS2s2Qy1Wa1RCZ1NTWmRGRTluUVVreWM1dnpjY2haZnloS2l2YThheUhLNmhHaGxBSk9hSl9XS25fbkR1Y05lblhLY0p3Nmp3T2Q3NDEwYXkyczVITVFacTFsMmdaTXpwbU5vS0N2ZUpMUTByTkFveFpBNUhLVmlhZjlWbm1DNE9vbg?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ36" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR36" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS36" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT36" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026</t>
-        </is>
-      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>503-897-0236</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001863768</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UBS Global Family Office</t>
+          <t>Covenant Multifamily Offices, Llc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>firm's own name states multi-family: 'Covenant Multifamily Offices, Llc'; files SEC 13F-HR as 'Covenant Multifamily Offices, Llc' (SEC 13F-HR 2021-10-21 (CIK 0001599749))</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>18756 STONE OAK PARKWAY, SUITE 102, SAN ANTONIO, TX, 78258</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -7125,37 +7705,41 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>$556.9M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
@@ -7163,44 +7747,72 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Kristina Craig</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr"/>
       <c r="AY37" t="inlineStr"/>
@@ -7213,52 +7825,52 @@
       <c r="BF37" t="inlineStr"/>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
-      <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="inlineStr"/>
-      <c r="BL37" t="inlineStr"/>
-      <c r="BM37" t="inlineStr"/>
-      <c r="BN37" t="inlineStr"/>
-      <c r="BO37" t="inlineStr">
-        <is>
-          <t>UBS Global Family Office Report 2024: balance is back - Funds Society</t>
-        </is>
-      </c>
-      <c r="BP37" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdGVESWZUelkteVdzNzZHdlF2QUM1cHFlYUppOTYxSkJoVWp2QklYU1lnOTlWaTdUcm9ncjZKWGpUOEhVS2FUNWI5ZzZocUI3TkU5Y3JjTWJGWHh5T2hkX2l5S2puOU01NndUZzhtX2ttbF9lLXk3cEtsTE5XV1k1WEJmRHd4YV9YS2ZKbjlrLTZQblVMb0RfRkJrakNYNjg?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ37" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR37" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS37" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT37" t="inlineStr">
-        <is>
-          <t>Thu, 23 May 2024</t>
-        </is>
-      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>210-403-5350</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001599749</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN37" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kirloskar Family Office</t>
+          <t>Cva Family Office, Llc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7268,15 +7880,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>255 FILLMORE STREET, SUITE 500, DENVER, CO, 80206</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -7289,37 +7901,41 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>For a period of over 135+ years, we at the Kirloskar Group, affectionately referred to as Kirloskar, have focused on the progress of economic self-sufficiency and industrial growth in India. Our first products, the iron plough and chaff cutters, were introduced by our founder Hon. Late Shri Laxmanra</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>$949.6M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
@@ -7327,44 +7943,72 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>Welcome to the official website of Kirloskar, Explore the legacy of Kirloskar Group - Your trusted source for information about Kirloskar Companies with over 135 + years of industrial excellence</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Dalyce Tinoco</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Dir of Wealth Advisory</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr"/>
       <c r="AY38" t="inlineStr"/>
@@ -7377,47 +8021,47 @@
       <c r="BF38" t="inlineStr"/>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
-      <c r="BI38" t="inlineStr"/>
-      <c r="BJ38" t="inlineStr"/>
-      <c r="BK38" t="inlineStr"/>
-      <c r="BL38" t="inlineStr"/>
-      <c r="BM38" t="inlineStr"/>
-      <c r="BN38" t="inlineStr"/>
-      <c r="BO38" t="inlineStr">
-        <is>
-          <t>Kirloskar Family Office, Madhusudan Kela back Artha Group’s Rs 450 cr micro-VC fund - Business Today</t>
-        </is>
-      </c>
-      <c r="BP38" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNVkl5WXV3Q2liTG0tcXRrOW5hNnlMdmQ4WW5TQXZNVVBLZ2VNTVhTV0NnV3FFOHUxYWljQW5lN09zemxEQXdfam5PT1I3cUNQRWZKZE1ycFhZWDRxa1FlV09LWnlBWHFuaTdyVEFQM3NFejlQWVJWaWxjdVp5Q0o5dnhsNmdaNzZtWHVNUEdQQlh5eWRrNGdMQ2RiN1pFVVJteGFMcC1wYlNGSWRZQlo5WThzaUFKT25hdENBbkdHaGNTSmZFVlVQdHlPX0hkV1k5QWxkLVB3elRveVdpRG1Ja2kxMUZ3Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ38" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR38" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT38" t="inlineStr">
-        <is>
-          <t>Tue, 11 Oct 2022</t>
-        </is>
-      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>3032435611</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001802084</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM38" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="BO38" t="inlineStr"/>
+      <c r="BP38" t="inlineStr"/>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Allie Family Office Llc</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7432,13 +8076,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
+          <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -7455,12 +8099,12 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>$228.5M (13F portfolio value)</t>
+          <t>$123.6M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -7480,7 +8124,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -7501,20 +8145,44 @@
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Matt Dino</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -7534,7 +8202,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr"/>
@@ -7551,12 +8219,12 @@
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>7866357162</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001908612</t>
+          <t>SEC EDGAR submissions CIK 0001596197</t>
         </is>
       </c>
       <c r="BK39" t="inlineStr">
@@ -7576,7 +8244,7 @@
       </c>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr"/>
@@ -7589,7 +8257,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Capitol Family Office, Inc.</t>
+          <t>Louis-Dreyfus Family Office Llc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7604,13 +8272,13 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1500 NW BETHANY BLVD., SUITE 200, BEAVERTON, OR, 97006</t>
+          <t>10 WESTPORT ROAD, STE C-201, PO BOX 690, WILTON, CT, 06897</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -7627,12 +8295,12 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>$84.7M (13F portfolio value)</t>
+          <t>$64.7M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -7652,7 +8320,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -7673,20 +8341,44 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>W. Thomas Wingertzahn</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>CCO</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -7706,7 +8398,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr"/>
@@ -7723,12 +8415,12 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>503-897-0236</t>
+          <t>203-762-6135</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001863768</t>
+          <t>SEC EDGAR submissions CIK 0001889527</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
@@ -7748,7 +8440,7 @@
       </c>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr"/>
@@ -7761,7 +8453,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Covenant Multifamily Offices, Llc</t>
+          <t>Marcuard Family Office Ltd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7771,18 +8463,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>firm's own name states multi-family: 'Covenant Multifamily Offices, Llc'</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://marcuardfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>18756 STONE OAK PARKWAY, SUITE 102, SAN ANTONIO, TX, 78258</t>
+          <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -7799,12 +8495,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>$556.9M (13F portfolio value)</t>
+          <t>$46.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -7824,7 +8520,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2014-10-16</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -7853,12 +8549,12 @@
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Managing Partner &amp;amp; Assistant Vice President</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7878,7 +8574,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2014-10-16</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr"/>
@@ -7895,12 +8591,12 @@
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>210-403-5350</t>
+          <t>41 43 344 60 00</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001599749</t>
+          <t>SEC EDGAR submissions CIK 0001538112</t>
         </is>
       </c>
       <c r="BK41" t="inlineStr">
@@ -7920,7 +8616,7 @@
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2014-10-16</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr"/>
@@ -7933,7 +8629,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cva Family Office, Llc</t>
+          <t>Oneascent Family Office, Llc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7948,13 +8644,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>255 FILLMORE STREET, SUITE 500, DENVER, CO, 80206</t>
+          <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -7971,12 +8667,12 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>$949.65B (13F portfolio value)</t>
+          <t>$143.2M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -7996,7 +8692,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -8017,20 +8713,44 @@
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Ashleigh Swayze</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>Dir of Wealth Advisory</t>
+          <t>Counsel</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -8050,7 +8770,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr"/>
@@ -8067,12 +8787,12 @@
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>3032435611</t>
+          <t>2053139142</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001802084</t>
+          <t>SEC EDGAR submissions CIK 0002055812</t>
         </is>
       </c>
       <c r="BK42" t="inlineStr">
@@ -8092,7 +8812,7 @@
       </c>
       <c r="BN42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="BO42" t="inlineStr"/>
@@ -8105,7 +8825,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Intrepid Family Office Llc</t>
+          <t>Standard Family Office Llc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8120,13 +8840,13 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
+          <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -8143,12 +8863,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>$123.6M (13F portfolio value)</t>
+          <t>$96.8M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -8168,7 +8888,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -8189,20 +8909,44 @@
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Kelsey Olson</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -8222,7 +8966,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr"/>
@@ -8239,12 +8983,12 @@
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>(203) 862-3372</t>
+          <t>6054967760</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001596197</t>
+          <t>SEC EDGAR submissions CIK 0001809494</t>
         </is>
       </c>
       <c r="BK43" t="inlineStr">
@@ -8264,7 +9008,7 @@
       </c>
       <c r="BN43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO43" t="inlineStr"/>
@@ -8277,7 +9021,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office Llc</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8292,13 +9036,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10 WESTPORT ROAD, STE C-201, PO BOX 690, WILTON, CT, 06897</t>
+          <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -8315,12 +9059,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>$64.7M (13F portfolio value)</t>
+          <t>$615.8M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -8340,7 +9084,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -8361,20 +9105,44 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Mary Sigler</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -8394,7 +9162,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr"/>
@@ -8411,12 +9179,12 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>203-762-6135</t>
+          <t>949-721-2330</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001889527</t>
+          <t>SEC EDGAR submissions CIK 0001599603</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
@@ -8436,7 +9204,7 @@
       </c>
       <c r="BN44" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="BO44" t="inlineStr"/>
@@ -8449,12 +9217,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oneascent Family Office, Llc</t>
+          <t>UBS Family Office</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8464,15 +9232,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
-        </is>
-      </c>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -8485,41 +9253,37 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>$143.16B (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
@@ -8527,11 +9291,31 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
@@ -8539,36 +9323,12 @@
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Counsel</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV45" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="inlineStr"/>
@@ -8581,52 +9341,52 @@
       <c r="BF45" t="inlineStr"/>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
-      <c r="BI45" t="inlineStr">
-        <is>
-          <t>2053139142</t>
-        </is>
-      </c>
-      <c r="BJ45" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002055812</t>
-        </is>
-      </c>
-      <c r="BK45" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM45" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN45" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="BO45" t="inlineStr"/>
-      <c r="BP45" t="inlineStr"/>
-      <c r="BQ45" t="inlineStr"/>
-      <c r="BR45" t="inlineStr"/>
-      <c r="BS45" t="inlineStr"/>
-      <c r="BT45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+      <c r="BO45" t="inlineStr">
+        <is>
+          <t>UBS Family Office Report Highlights Strong US Exposure, AI Investment - Family Wealth Report</t>
+        </is>
+      </c>
+      <c r="BP45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWUF1RHNZRmdaSm5HanF5d3M5QWNja2NaVmNnN3RMcE85NVZxWnJnTlpTdkU5ODVWWlQxS2s2Qy1Wa1RCZ1NTWmRGRTluUVVreWM1dnpjY2haZnloS2l2YThheUhLNmhHaGxBSk9hSl9XS25fbkR1Y05lblhLY0p3Nmp3T2Q3NDEwYXkyczVITVFacTFsMmdaTXpwbU5vS0N2ZUpMUTByTkFveFpBNUhLVmlhZjlWbm1DNE9vbg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ45" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT45" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, Llc</t>
+          <t>UBS Global Family Office</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8636,15 +9396,15 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3323 NE 163RD STREET, SUITE 604, NORTH MIAMI BEACH, FL, 33160</t>
-        </is>
-      </c>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -8657,41 +9417,37 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>$155.7M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -8699,11 +9455,31 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
@@ -8711,36 +9487,12 @@
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>COUNSEL</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV46" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="inlineStr"/>
@@ -8753,52 +9505,52 @@
       <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
-      <c r="BI46" t="inlineStr">
-        <is>
-          <t>305-935-5502</t>
-        </is>
-      </c>
-      <c r="BJ46" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002135110</t>
-        </is>
-      </c>
-      <c r="BK46" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM46" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN46" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="BO46" t="inlineStr"/>
-      <c r="BP46" t="inlineStr"/>
-      <c r="BQ46" t="inlineStr"/>
-      <c r="BR46" t="inlineStr"/>
-      <c r="BS46" t="inlineStr"/>
-      <c r="BT46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr">
+        <is>
+          <t>UBS Global Family Office Report 2024: balance is back - Funds Society</t>
+        </is>
+      </c>
+      <c r="BP46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdGVESWZUelkteVdzNzZHdlF2QUM1cHFlYUppOTYxSkJoVWp2QklYU1lnOTlWaTdUcm9ncjZKWGpUOEhVS2FUNWI5ZzZocUI3TkU5Y3JjTWJGWHh5T2hkX2l5S2puOU01NndUZzhtX2ttbF9lLXk3cEtsTE5XV1k1WEJmRHd4YV9YS2ZKbjlrLTZQblVMb0RfRkJrakNYNjg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT46" t="inlineStr">
+        <is>
+          <t>Thu, 23 May 2024</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Standard Family Office Llc</t>
+          <t>Kirloskar Family Office</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8808,15 +9560,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
-        </is>
-      </c>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -8829,41 +9581,37 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>$96.8M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>For a period of over 135+ years, we at the Kirloskar Group, affectionately referred to as Kirloskar, have focused on the progress of economic self-sufficiency and industrial growth in India. Our first products, the iron plough and chaff cutters, were introduced by our founder Hon. Late Shri Laxmanra</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -8871,11 +9619,31 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Welcome to the official website of Kirloskar, Explore the legacy of Kirloskar Group - Your trusted source for information about Kirloskar Companies with over 135 + years of industrial excellence</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
@@ -8883,36 +9651,12 @@
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>Chief Compliance Officer</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV47" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="inlineStr"/>
@@ -8925,47 +9669,47 @@
       <c r="BF47" t="inlineStr"/>
       <c r="BG47" t="inlineStr"/>
       <c r="BH47" t="inlineStr"/>
-      <c r="BI47" t="inlineStr">
-        <is>
-          <t>6054967760</t>
-        </is>
-      </c>
-      <c r="BJ47" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001809494</t>
-        </is>
-      </c>
-      <c r="BK47" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM47" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN47" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="BO47" t="inlineStr"/>
-      <c r="BP47" t="inlineStr"/>
-      <c r="BQ47" t="inlineStr"/>
-      <c r="BR47" t="inlineStr"/>
-      <c r="BS47" t="inlineStr"/>
-      <c r="BT47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
+      <c r="BO47" t="inlineStr">
+        <is>
+          <t>Kirloskar Family Office, Madhusudan Kela back Artha Group’s Rs 450 cr micro-VC fund - Business Today</t>
+        </is>
+      </c>
+      <c r="BP47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNVkl5WXV3Q2liTG0tcXRrOW5hNnlMdmQ4WW5TQXZNVVBLZ2VNTVhTV0NnV3FFOHUxYWljQW5lN09zemxEQXdfam5PT1I3cUNQRWZKZE1ycFhZWDRxa1FlV09LWnlBWHFuaTdyVEFQM3NFejlQWVJWaWxjdVp5Q0o5dnhsNmdaNzZtWHVNUEdQQlh5eWRrNGdMQ2RiN1pFVVJteGFMcC1wYlNGSWRZQlo5WThzaUFKT25hdENBbkdHaGNTSmZFVlVQdHlPX0hkV1k5QWxkLVB3elRveVdpRG1Ja2kxMUZ3Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ47" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR47" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS47" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT47" t="inlineStr">
+        <is>
+          <t>Tue, 11 Oct 2022</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Pioneer Family Office, Llc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8980,13 +9724,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
+          <t>3323 NE 163RD STREET, SUITE 604, NORTH MIAMI BEACH, FL, 33160</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -9003,12 +9747,12 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>$615.8M (13F portfolio value)</t>
+          <t>$155.7M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -9028,7 +9772,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -9057,12 +9801,12 @@
       <c r="AP48" t="inlineStr"/>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>COUNSEL</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -9082,7 +9826,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr"/>
@@ -9099,12 +9843,12 @@
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>949-721-2330</t>
+          <t>305-935-5502</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001599603</t>
+          <t>SEC EDGAR submissions CIK 0002135110</t>
         </is>
       </c>
       <c r="BK48" t="inlineStr">
@@ -9124,7 +9868,7 @@
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr"/>

--- a/data/final/dataset.xlsx
+++ b/data/final/dataset.xlsx
@@ -781,12 +781,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stenger Family Office, Llc</t>
+          <t>DFO Management</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -796,23 +796,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106)); single- vs multi-family unproven</t>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://stengerfamilyoffice.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>https://www.dellfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/msd-capital</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026</t>
+          <t>Tue, 24 Feb 2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -829,41 +829,37 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>$629.4M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>MSD Capital, L.P. Established in 1998, exclusively manages the assets of Michael S. Dell and his family. MSD Capital utilizes a multi-disciplinary investment strategy focused on maximizing long-term capital appreciation by making investments across the globe in the equities of public and private com</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://www.dellfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
@@ -871,72 +867,44 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>DFO Management - Welcome About DFO Leadership Michael Dell Contacts About DFO Leadership Michael Dell Contacts DFO Management Learn More MSD Capital, L.P. Established in 1998, exclusively manages the assets of Michael S. Dell and his family. MSD Capital utilizes a multi-disciplinary investment strategy focused on maximizing long-term capital appreciation by making investments across the globe in t</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>https://www.dellfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Julia Patricia Foran</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Vice President, Operations</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
@@ -945,12 +913,12 @@
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
+          <t>inquiries@dellfamilyoffice.com</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>https://stengerfamilyoffice.com</t>
+          <t>https://www.dellfamilyoffice.com</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -975,42 +943,38 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>630-912-8295</t>
+          <t>(212) 303-1650</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002056106</t>
+          <t>https://www.dellfamilyoffice.com</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>official SEC filing (business phone)</t>
+          <t>scraped from site (unverified)</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>Stenger Family Office LLC Has $28.84 Million Holdings in Microsoft Corporation $MSFT - MarketBeat</t>
+          <t>Snow crab in N.L. could reach 'historic lows' by 2028, reports DFO - CBC</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcEd4UEw5VkZiVEt5a1lCQnl5NTdxNFVWUDVad0N4ODFySUtCZUFOcnhaSHhLN2lodVA2T1BGQnN5RlZOWXFoYnpDdVY1bkd0bGZ5c25jaW01Mk96NnVzN2hkMVB0Q3UxMEhBdUtZMjBNU1BPS3p1aENKQUJxSUdtYklGQVFQcGQ0TjdhUmYtYzU3cURLZzBrc0pvZ0tGMXhqZm94cGlHS1BTbWc4eVd3YkhVYzNkLTlhYlBnV2FDQXhDd0pwVFpZV0I4bWItVlNFNGFPNjlxR1BMQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNam04X0xZLU82TjByc0JzLUhwVTcxWEo4dWdVbDV4anJxTEdwQm45cU0yUi1RNXE1QmpmMjExT2MzVTZTUF9WSzJEZUh1ejlCbUl4YnBKSDhCalAwMlM1SHZKX19waVVnVlRmdlEyb0JMTXFvdHJLU2QySkpOXzRCNVJXcXFreC15Y0l4Y0tVWQ?oc=5</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1030,14 +994,14 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>Wed, 22 Jul 2026</t>
+          <t>Tue, 24 Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fiduciary Family Office, Llc</t>
+          <t>Stenger Family Office, Llc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1052,23 +1016,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Stenger Family Office, Llc' (SEC 13F-HR 2026-07-13 (CIK 0002056106)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://fiduciaryfo.com</t>
+          <t>https://stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
+          <t>NAPERVILLE FINANCIAL CENTER, 400 EAST DIEHL RD, SUITE 550, NAPERVILLE, IL, 60563</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fri, 21 Nov 2025</t>
+          <t>Wed, 22 Jul 2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1087,12 +1051,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>$350.8M (13F portfolio value)</t>
+          <t>$629.4M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1112,7 +1076,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -1133,20 +1097,44 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Julia Patricia Foran</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Vice President, Operations</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1166,7 +1154,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr"/>
@@ -1177,12 +1165,12 @@
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>admin@fiduciaryfo.com</t>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>https://fiduciaryfo.com</t>
+          <t>https://stengerfamilyoffice.com</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1207,12 +1195,12 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>(561) 353-4440</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002020280</t>
+          <t>SEC EDGAR submissions CIK 0002056106</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1232,17 +1220,17 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>Fiduciary Family Office, LLC - bocaratonobserver.com</t>
+          <t>Stenger Family Office LLC Has $28.84 Million Holdings in Microsoft Corporation $MSFT - MarketBeat</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5hMDdCbHRNSXhyNENZbmZNbWJxTGEtMjdOWTY3M3VVaThfMXdtRVBUeTZpaWZEMFdBLU9wbENsN3BHRnhkQXRUOUxKeFF5TmZsY2VPTXM2MXJiYkxqLTZrZnFETnVLTVVnYnh1VUFub0dMTHRYbUHSAYABQVVfeXFMUGhUTnRRSnk3T2c4YWM0eGUyQnowS2R6cEI0SjZpMGFXd3VVZ0RqdklEZFhacEtLYjRnV0ZPam9mVmwzN0FCUWlydTVkS0Q0S0N5b1VjaEpzOUgzUHV2UzNSNzRwYTRQRGE2M202ZlNuN2RrY3Nkc3ptWkIxc055S2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQcEd4UEw5VkZiVEt5a1lCQnl5NTdxNFVWUDVad0N4ODFySUtCZUFOcnhaSHhLN2lodVA2T1BGQnN5RlZOWXFoYnpDdVY1bkd0bGZ5c25jaW01Mk96NnVzN2hkMVB0Q3UxMEhBdUtZMjBNU1BPS3p1aENKQUJxSUdtYklGQVFQcGQ0TjdhUmYtYzU3cURLZzBrc0pvZ0tGMXhqZm94cGlHS1BTbWc4eVd3YkhVYzNkLTlhYlBnV2FDQXhDd0pwVFpZV0I4bWItVlNFNGFPNjlxR1BMQQ?oc=5</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1262,14 +1250,14 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>Fri, 21 Nov 2025</t>
+          <t>Wed, 22 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deutsche Oppenheim Family Office Ag</t>
+          <t>Fiduciary Family Office, Llc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1279,28 +1267,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>bank/wirehouse-affiliated SEC-registered family office (CIK 0001759113, verified filing address/phone)</t>
+          <t>files SEC 13F-HR as 'Fiduciary Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002020280)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://deutsche-oppenheim.de</t>
+          <t>https://fiduciaryfo.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11 OPPENHEIM STREET, COLOGNE, 2M, 50668</t>
+          <t>150 EAST PALMETTO PARK ROAD, SUITE 301, BOCA RATON, FL, 33432</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026</t>
+          <t>Fri, 21 Nov 2025</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1317,12 +1305,36 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>$350.8M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1347,12 +1359,36 @@
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2020280/000117266126001820/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
@@ -1361,12 +1397,12 @@
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>info@deutsche-oppenheim.de</t>
+          <t>admin@fiduciaryfo.com</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>https://deutsche-oppenheim.de</t>
+          <t>https://fiduciaryfo.com</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1391,12 +1427,12 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>49221577720</t>
+          <t>(561) 353-4440</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001759113</t>
+          <t>SEC EDGAR submissions CIK 0002020280</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -1416,17 +1452,17 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>Deutsche Bank expands and strengthens its ultra-high net worth coverage - Deutsche Bank AG</t>
+          <t>Fiduciary Family Office, LLC - bocaratonobserver.com</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNd0M0eWdIeE5xMHczWTd0bEsxaDFLWm05aUFEZ2lRMGUtMks3UmJUYmVhWDM0UDB4T2xTQkZKcGJHTUF0YVNjaFgxRGozamtNT2FiT0ZobmZ2WHNEMHNtclNzVEJIbGRqcnFQcEVqZFFVUVY4OHN2R0FNcW5FUU9lMW5iMzRMQTByMEVpbWNwS3YyUG0tX2I2ME1aNzQ5b0JvODdtZElSZFk3UjlTOWMyQURNQjExVFB6TldjRTlpa1dmQVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5hMDdCbHRNSXhyNENZbmZNbWJxTGEtMjdOWTY3M3VVaThfMXdtRVBUeTZpaWZEMFdBLU9wbENsN3BHRnhkQXRUOUxKeFF5TmZsY2VPTXM2MXJiYkxqLTZrZnFETnVLTVVnYnh1VUFub0dMTHRYbUHSAYABQVVfeXFMUGhUTnRRSnk3T2c4YWM0eGUyQnowS2R6cEI0SjZpMGFXd3VVZ0RqdklEZFhacEtLYjRnV0ZPam9mVmwzN0FCUWlydTVkS0Q0S0N5b1VjaEpzOUgzUHV2UzNSNzRwYTRQRGE2M202ZlNuN2RrY3Nkc3ptWkIxc055S2s?oc=5</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -1446,14 +1482,14 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026</t>
+          <t>Fri, 21 Nov 2025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aurelius Family Office Llc</t>
+          <t>Deutsche Oppenheim Family Office Ag</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1463,29 +1499,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Aurelius Family Office Llc' (SEC 13F-HR 2026-07-13 (CIK 0002053738)); single- vs multi-family unproven</t>
+          <t>bank/wirehouse-affiliated SEC-registered family office (CIK 0001759113, verified filing address/phone)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://aurelius.net</t>
+          <t>https://deutsche-oppenheim.de</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 EXECUTIVE PARK DR, SUITE 261, BEDFORD, NH, 03110</t>
+          <t>11 OPPENHEIM STREET, COLOGNE, 2M, 50668</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1493,36 +1537,12 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>$253.9M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1541,66 +1561,18 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Brenda Winslow</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Chief Compliance Officer</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
@@ -1609,12 +1581,12 @@
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>info@aurelius.net</t>
+          <t>info@deutsche-oppenheim.de</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>https://aurelius.net</t>
+          <t>https://deutsche-oppenheim.de</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -1639,12 +1611,12 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6036028550</t>
+          <t>49221577720</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002053738</t>
+          <t>SEC EDGAR submissions CIK 0001759113</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -1664,20 +1636,44 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>Deutsche Bank expands and strengthens its ultra-high net worth coverage - Deutsche Bank AG</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNd0M0eWdIeE5xMHczWTd0bEsxaDFLWm05aUFEZ2lRMGUtMks3UmJUYmVhWDM0UDB4T2xTQkZKcGJHTUF0YVNjaFgxRGozamtNT2FiT0ZobmZ2WHNEMHNtclNzVEJIbGRqcnFQcEVqZFFVUVY4OHN2R0FNcW5FUU9lMW5iMzRMQTByMEVpbWNwS3YyUG0tX2I2ME1aNzQ5b0JvODdtZElSZFk3UjlTOWMyQURNQjExVFB6TldjRTlpa1dmQVk?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cambient Family Office, Llc</t>
+          <t>Aurelius Family Office Llc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1692,17 +1688,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Cambient Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002105684)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Aurelius Family Office Llc' (SEC 13F-HR 2026-07-13 (CIK 0002053738)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://cambient.com</t>
+          <t>https://aurelius.net</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4690 FULTON STREET E, SUITE 203, ADA, MI, 49301</t>
+          <t>3 EXECUTIVE PARK DR, SUITE 261, BEDFORD, NH, 03110</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1719,12 +1715,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>$716.4M (13F portfolio value)</t>
+          <t>$253.9M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1744,7 +1740,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1767,12 +1763,12 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Josh Gibbs</t>
+          <t>Brenda Winslow</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1792,17 +1788,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Trust Advisor, Chief Compliance Officer</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2053738/000205373826000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1822,7 +1818,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr"/>
@@ -1833,12 +1829,12 @@
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>info@cambient.com</t>
+          <t>info@aurelius.net</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>https://cambient.com</t>
+          <t>https://aurelius.net</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -1863,12 +1859,12 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>(616) 330-2270</t>
+          <t>6036028550</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002105684</t>
+          <t>SEC EDGAR submissions CIK 0002053738</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -1888,7 +1884,7 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr"/>
@@ -1901,7 +1897,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Independent Family Office, Llc</t>
+          <t>Cambient Family Office, Llc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1916,17 +1912,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Independent Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0001756485)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Cambient Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002105684)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ifollc.com</t>
+          <t>https://cambient.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>677 BROADWAY, 7TH FLOOR, ALBANY, NY, 12207</t>
+          <t>4690 FULTON STREET E, SUITE 203, ADA, MI, 49301</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1943,12 +1939,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>$243.0M (13F portfolio value)</t>
+          <t>$716.4M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1968,7 +1964,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1991,12 +1987,12 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>William Reickert</t>
+          <t>Josh Gibbs</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2016,17 +2012,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Trust Advisor, Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2105684/000139834426006785/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2046,7 +2042,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr"/>
@@ -2057,12 +2053,12 @@
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>dr@ifollc.com</t>
+          <t>info@cambient.com</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>https://ifollc.com</t>
+          <t>https://cambient.com</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -2087,12 +2083,12 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>(518) 452-8050</t>
+          <t>(616) 330-2270</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001756485</t>
+          <t>SEC EDGAR submissions CIK 0002105684</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -2112,7 +2108,7 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr"/>
@@ -2125,12 +2121,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>Independent Family Office, Llc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2140,32 +2136,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'PATHSTONE FAMILY OFFICE, LLC' (SEC 13F-HR 2024-01-16 (CIK 0001511137)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Independent Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0001756485)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://pathstone.com</t>
+          <t>https://ifollc.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10 STERLING BLVD, SUITE 402, ENGLEWOOD, NJ, 07631</t>
+          <t>677 BROADWAY, 7TH FLOOR, ALBANY, NY, 12207</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2175,12 +2163,12 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>$7.03B (13F portfolio value)</t>
+          <t>$243.0M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2200,7 +2188,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -2223,12 +2211,12 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Lisandra Wilmott</t>
+          <t>William Reickert</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2248,17 +2236,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>General Counsel &amp;amp; CCO</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1756485/000195175726000873/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2278,7 +2266,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr"/>
@@ -2287,20 +2275,44 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>dr@ifollc.com</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>https://ifollc.com</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>201-731-7112</t>
+          <t>(518) 452-8050</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001511137</t>
+          <t>SEC EDGAR submissions CIK 0001756485</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -2320,49 +2332,25 @@
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>ShinyHunters Strikes Pathstone Family Office in Major Ransomware Attack - DeXpose</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPMG5VZTRWY1VHdkxNOVY3OHR5LW0yQnNYN2VPSDREUWhXNXJVTHJNSUhfUng0bEhNcEgwcGtLeGsyZWNFdzJlaDFBX18wUzhlSGVkbnE2WWlHdWFQSXJCS2tQMkNRUGI1OU5nOWxVTUtONkZKaUtKT3RnRC1zUUY3ay1NcG00YmgyczJ2RmlhbVB2UFRTMGZnWDR0cw?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>targeted news query</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026</t>
-        </is>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, Llc</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>SEC EDGAR full-text search</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2372,23 +2360,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Arrowroot Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0002017744)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'PATHSTONE FAMILY OFFICE, LLC' (SEC 13F-HR 2024-01-16 (CIK 0001511137)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com</t>
+          <t>https://pathstone.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4553 GLENCOE AVENUE, SUITE 200, MARINA DEL REY, CA, 90292</t>
+          <t>10 STERLING BLVD, SUITE 402, ENGLEWOOD, NJ, 07631</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026</t>
+          <t>Fri, 27 Feb 2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2407,12 +2395,12 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>$302.5M (13F portfolio value)</t>
+          <t>$7.03B (13F portfolio value)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2432,7 +2420,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -2455,12 +2443,12 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Roberto Santos</t>
+          <t>Lisandra Wilmott</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2480,17 +2468,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>General Counsel &amp;amp; CCO</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1511137/000108514624000248/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2510,7 +2498,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr"/>
@@ -2527,12 +2515,12 @@
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>201-731-7112</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002017744</t>
+          <t>SEC EDGAR submissions CIK 0001511137</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -2552,17 +2540,17 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC's iShares U.S. Treasury Bond ETF(GOVT) Holding History - GuruFocus</t>
+          <t>ShinyHunters Strikes Pathstone Family Office in Major Ransomware Attack - DeXpose</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdzloS3pOS1RwMFRYMmotX1lOSHQwXzlialdKR0t6UG05VDNfVldMR21KZWdBV0pCUEV4eEp4cjdJYzdjQXBIWmhEcG9MZk5wY1hOLWMyTF9zOE5QM0IyMXg3LTdKaVlZeDE1SU1ONlhQY2MydEZzVG14c1piQk5tcW00SVdYZkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPMG5VZTRWY1VHdkxNOVY3OHR5LW0yQnNYN2VPSDREUWhXNXJVTHJNSUhfUng0bEhNcEgwcGtLeGsyZWNFdzJlaDFBX18wUzhlSGVkbnE2WWlHdWFQSXJCS2tQMkNRUGI1OU5nOWxVTUtONkZKaUtKT3RnRC1zUUY3ay1NcG00YmgyczJ2RmlhbVB2UFRTMGZnWDR0cw?oc=5</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -2582,14 +2570,14 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026</t>
+          <t>Fri, 27 Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, Llc</t>
+          <t>Arrowroot Family Office, Llc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2604,23 +2592,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Fortitude Family Office, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001950506)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Arrowroot Family Office, Llc' (SEC 13F-HR 2026-05-15 (CIK 0002017744)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com</t>
+          <t>https://arrowrootfamilyoffice.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7500 N DOBSON RD, SUITE 151, SCOTTSDALE, AZ, 85256</t>
+          <t>4553 GLENCOE AVENUE, SUITE 200, MARINA DEL REY, CA, 90292</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026</t>
+          <t>Tue, 14 Jul 2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,12 +2627,12 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>$516.0M (13F portfolio value)</t>
+          <t>$302.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2664,7 +2652,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -2687,12 +2675,12 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Drew Phillips</t>
+          <t>Roberto Santos</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2712,17 +2700,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2742,7 +2730,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr"/>
@@ -2759,12 +2747,12 @@
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>602-834-0089</t>
+          <t>310.341.4774</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001950506</t>
+          <t>SEC EDGAR submissions CIK 0002017744</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -2784,17 +2772,17 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC's Avantis Total Equity Markets(AVTM) Holding History - GuruFocus</t>
+          <t>Arrowroot Family Office, LLC's iShares U.S. Treasury Bond ETF(GOVT) Holding History - GuruFocus</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTlZLRUVod3Z0ZzJ0VjM5Z0xIOE5iM3pKNnVVMGlxdjdjWkM1QzExOGxpLVVJb3RGQnRuYjBPMVc2WTEta21SQ2JXMDRlbEtTVGFnVjdtc2V1V0t3eWkyOUNIaGw5ZlNBanRwVjZzaG9TTjlzU08zanhQcE52M19VRHM3OXBqU0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdzloS3pOS1RwMFRYMmotX1lOSHQwXzlialdKR0t6UG05VDNfVldMR21KZWdBV0pCUEV4eEp4cjdJYzdjQXBIWmhEcG9MZk5wY1hOLWMyTF9zOE5QM0IyMXg3LTdKaVlZeDE1SU1ONlhQY2MydEZzVG14c1piQk5tcW00SVdYZkk?oc=5</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -2814,19 +2802,19 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026</t>
+          <t>Tue, 14 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Fortitude Family Office, Llc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2836,24 +2824,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Duquesne Family Office LLC' (SEC 13F-HR 2026-05-15 (CIK 0001536411)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Fortitude Family Office, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001950506)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://fortitudefo.com</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40 WEST 57TH STREET, 25TH FLOOR, NEW YORK, NY, 10019</t>
+          <t>7500 N DOBSON RD, SUITE 151, SCOTTSDALE, AZ, 85256</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026</t>
+          <t>Sun, 26 Jul 2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>investment</t>
+          <t>news</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2867,12 +2859,12 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>$3.38B (13F portfolio value)</t>
+          <t>$516.0M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2892,7 +2884,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -2915,12 +2907,12 @@
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Sue Meng</t>
+          <t>Drew Phillips</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2940,17 +2932,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>General Counsel</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1950506/000195050626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2970,7 +2962,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr"/>
@@ -2987,12 +2979,12 @@
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>(212) 830-6500</t>
+          <t>602-834-0089</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001536411</t>
+          <t>SEC EDGAR submissions CIK 0001950506</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -3012,17 +3004,17 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>Duquesne Family Office Ups Micron Technology Stake by 23,400 Shares - The Globe and Mail</t>
+          <t>Fortitude Family Office, LLC's Avantis Total Equity Markets(AVTM) Holding History - GuruFocus</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNWlU5Z3dHWl9KNkFKSHhKdW1US0dmalZVNWdsb2lkV25kMjdYN2FKaFFyZlp5SzZGR3FWZmtCc1pGbUdwV3NMb201aFlTa29LcGdkUE5NZ3NtTk5mRXlDMXhXVUQ1Vm51R1hBMmxlcXN0eFJYWkVIbDR2ekppZi1nekNMNXlOTVBYQkhIRHcyNmh3a0FKRWpfNnVrN2QtUGVSc0FmSDctM0lVSkQ2MEVHN2NMNlItMWdsMWEyTzJqVlBLdU9jX1BDckFrQVpZY3lWb3V0ald1eG1MdmFGNTRCbVV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTlZLRUVod3Z0ZzJ0VjM5Z0xIOE5iM3pKNnVVMGlxdjdjWkM1QzExOGxpLVVJb3RGQnRuYjBPMVc2WTEta21SQ2JXMDRlbEtTVGFnVjdtc2V1V0t3eWkyOUNIaGw5ZlNBanRwVjZzaG9TTjlzU08zanhQcE52M19VRHM3OXBqU0E?oc=5</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -3042,19 +3034,19 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026</t>
+          <t>Sun, 26 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pmg Family Office Llc</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>SEC EDGAR full-text search</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3064,19 +3056,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Pmg Family Office Llc' (SEC 13F-HR 2026-07-16 (CIK 0002102299)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Duquesne Family Office LLC' (SEC 13F-HR 2026-05-15 (CIK 0001536411)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5700 W PLANO PARKWAY, SUITE 2600, PLANO, TX, 75093</t>
+          <t>40 WEST 57TH STREET, 25TH FLOOR, NEW YORK, NY, 10019</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sun, 22 Mar 2026</t>
+          <t>Fri, 29 May 2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3095,12 +3087,12 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>$108.5M (13F portfolio value)</t>
+          <t>$3.38B (13F portfolio value)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -3120,7 +3112,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -3141,20 +3133,44 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Sue Meng</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>General Counsel</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -3174,7 +3190,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr"/>
@@ -3191,12 +3207,12 @@
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>2145508790</t>
+          <t>(212) 830-6500</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002102299</t>
+          <t>SEC EDGAR submissions CIK 0001536411</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -3216,17 +3232,17 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>PMG Family Office buys 3,064 Apple shares worth $780K amid positive analyst outlooks. - Pluang</t>
+          <t>Duquesne Family Office Ups Micron Technology Stake by 23,400 Shares - The Globe and Mail</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5GbC0zREhIb1hfU2FLX0hFbV9UR0V5ZHdhbGZ0cmJHejR4dHY4V2lkWS1wdFZXdDNsalFxOHJPZzZGS0p3ajR5alh1ME5ka1hfOFFZalJoWmhUbXN4Q21XRGlLSkhyLTRWd09uWXZnd29SU1Z1dzFaMDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNWlU5Z3dHWl9KNkFKSHhKdW1US0dmalZVNWdsb2lkV25kMjdYN2FKaFFyZlp5SzZGR3FWZmtCc1pGbUdwV3NMb201aFlTa29LcGdkUE5NZ3NtTk5mRXlDMXhXVUQ1Vm51R1hBMmxlcXN0eFJYWkVIbDR2ekppZi1nekNMNXlOTVBYQkhIRHcyNmh3a0FKRWpfNnVrN2QtUGVSc0FmSDctM0lVSkQ2MEVHN2NMNlItMWdsMWEyTzJqVlBLdU9jX1BDckFrQVpZY3lWb3V0ald1eG1MdmFGNTRCbVV3?oc=5</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -3246,19 +3262,19 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>Sun, 22 Mar 2026</t>
+          <t>Fri, 29 May 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lexington Family Office &amp; Trust, Llc</t>
+          <t>Prime Opportunities Investment Group</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3268,24 +3284,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001551648) with verified filing address/phone; single- vs multi-family split unproven</t>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://lex-life.com</t>
+          <t>http://www.primeopp.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9005 OVERLOOK BLVD., BRENTWOOD, TN, 37027</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3293,29 +3309,109 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>$5 billion</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>http://www.primeopp.com</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>site copy near AUM/assets language (unverified)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>The contents of this website have been prepared for informational purposes only without regard to the investment objectives, financial situation, or means of any particular person or entity, and PRIME is not soliciting any action based upon them. No information included on this website is to be cons</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>http://www.primeopp.com</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Compare that value to the current stock price (target 2x-3x current value), to determine the caliber of the investment opportunity;</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>http://www.primeopp.com</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>site copy (mandate/criteria language)</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Home - This is Prime Access Notice By clicking "I Agree" you are confirming that you are an Accredited Investor. Verification of your accredited status grants you 30 days of access to exclusive content. If you do not meet accredited investor criteria, kindly close this pop-up to explore the remainder of our website. The following notices explain certain restrictions imposed by law on the distribut</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>http://www.primeopp.com</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
@@ -3335,66 +3431,38 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>team@lex-life.com</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>https://lex-life.com</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>+1 800 550 4188</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>http://www.primeopp.com</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>scraped from site (unverified)</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
         <is>
           <t>inference</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>386-566-7249</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001551648</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>2012-06-18</t>
-        </is>
-      </c>
+      <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr"/>
       <c r="BQ13" t="inlineStr"/>
@@ -3405,7 +3473,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pointone Family Office, Llc</t>
+          <t>Pmg Family Office Llc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3420,24 +3488,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0002102280) with verified filing address/phone; single- vs multi-family split unproven</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://p1fo.com</t>
-        </is>
-      </c>
+          <t>files SEC 13F-HR as 'Pmg Family Office Llc' (SEC 13F-HR 2026-07-16 (CIK 0002102299)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>919 MANHATTAN AVENUE, SUITE 101, MANHATTAN BEACH, CA, 90266</t>
+          <t>5700 W PLANO PARKWAY, SUITE 2600, PLANO, TX, 75093</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sun, 22 Mar 2026</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3445,12 +3517,36 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>$108.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -3475,94 +3571,118 @@
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2102299/000208585326000755/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>info@p1fo.com</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>https://p1fo.com</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>MX record present (domain accepts mail)</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>2145508790</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002102299</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>PMG Family Office buys 3,064 Apple shares worth $780K amid positive analyst outlooks. - Pluang</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5GbC0zREhIb1hfU2FLX0hFbV9UR0V5ZHdhbGZ0cmJHejR4dHY4V2lkWS1wdFZXdDNsalFxOHJPZzZGS0p3ajR5alh1ME5ka1hfOFFZalJoWmhUbXN4Q21XRGlLSkhyLTRWd09uWXZnd29SU1Z1dzFaMDV3?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
         <is>
           <t>inference</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>8183973514</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002102280</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>Sun, 22 Mar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE OF AMERICA, INC.</t>
+          <t>Lexington Family Office &amp; Trust, Llc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3572,28 +3692,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001871181) with verified filing address/phone; single- vs multi-family split unproven</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>SEC-registered operating entity (CIK 0001551648) with verified filing address/phone; single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://lex-life.com</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6898 S. UNIVERSITY BLVD.,, SUITE 100, CENTENNIAL, CO, 80122</t>
+          <t>9005 OVERLOOK BLVD., BRENTWOOD, TN, 37027</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3619,36 +3735,12 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>SEC-registered filer; industry: Surgical &amp; Medical Instruments &amp; Apparatus.</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001871181</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>SEC entity record</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -3667,20 +3759,44 @@
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>team@lex-life.com</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>https://lex-life.com</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>303-874-7474</t>
+          <t>386-566-7249</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001871181</t>
+          <t>SEC EDGAR submissions CIK 0001551648</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
@@ -3700,68 +3816,52 @@
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>Enterprise value to revenue forward of Family Office of America Inc. – OTC:FOFA - TradingView</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQaklaZnEwRDJjU3ppT3VGZmU2cUlHZGpQa2xscGU0aWVCQkRZaWJDdGpJSHpJdGMzLUNZdTZLWmJyRXdxZ1ZPTTlGSmg2MS1BdHBIZDRuZGxvZUJSc1VTc2k1M09VRHRSWDdtMVROR1Vid05kRXNBeU1xaVJmRWptQmxlVlE3NXE5YWdvaHpCcEJkeE85eXY4MUJiRG1Ud1NjV29EUXVvajg?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>targeted news query</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026</t>
-        </is>
-      </c>
+          <t>2012-06-18</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AC Family Office</t>
+          <t>Pointone Family Office, Llc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>press names one individual behind the office ('Henry Pizzutello') [https://news.google.com/rss/articles/CBMi6wFBVV95cUxQLW1hX3hlQVlSYnVycDVTbkhyTTRXUjJBTWtkalVZSFpJc29OMVFQeEgzVWRCM3VVTlBCX0prNEtnbXhybEZuaC04Y3AzMFRrYjgteldQRk1adk5rNVJzVUlHVDg0eU9tYm1ZdGRvOTlxRTg3b3AzY292THJLNVlQaGJSMzVmdTIzZDk0TWJEWWN0ZmRFanBqbm1XY0tibmpGTU9zT3J6dGktTTZYYzlpOFd0T2Q5X3F5OG1xMGhZUVVIbUhSRkg5ZERpMXA2VGdKZHZWQldLMXo3NXBFbVZtNFJObzJCdi1ueGtB?oc=5] (inference/medium)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>SEC-registered operating entity (CIK 0002102280) with verified filing address/phone; single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://p1fo.com</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>919 MANHATTAN AVENUE, SUITE 101, MANHATTAN BEACH, CA, 90266</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3793,36 +3893,12 @@
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Henry Pizzutello</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQLW1hX3hlQVlSYnVycDVTbkhyTTRXUjJBTWtkalVZSFpJc29OMVFQeEgzVWRCM3VVTlBCX0prNEtnbXhybEZuaC04Y3AzMFRrYjgteldQRk1adk5rNVJzVUlHVDg0eU9tYm1ZdGRvOTlxRTg3b3AzY292THJLNVlQaGJSMzVmdTIzZDk0TWJEWWN0ZmRFanBqbm1XY0tibmpGTU9zT3J6dGktTTZYYzlpOFd0T2Q5X3F5OG1xMGhZUVVIbUhSRkg5ZERpMXA2VGdKZHZWQldLMXo3NXBFbVZtNFJObzJCdi1ueGtB?oc=5</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>named in news headline (unverified)</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Wed, 20 May 2026</t>
-        </is>
-      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
@@ -3835,75 +3911,119 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>AC Family Office Recruits Henry Pizzutello to Expand Presence in The Woodlands and Beaumont Regions - Morningstar</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPeGpUbkI4NXJYV052dVlvZnlIY0x1cGZJM3Y3ckRyUFk1RExDYWFoVGVjaDd5R1NKWEdZYmFkaGdjZzNxMlRRRGNNSDdSMGg0bGNESUoyUUNNajgzWFFZN0RZR1p5RkgyQlk2ejF6VjRIOE5BcnhHMUtzbTVjcmZNdGpKelFsZkFXaThlZ294c1BjTDVJMVljTmxSYndGOGFQRjVLT3cyRWM2X01xZlpjX3duRHhxY2lBcnJWZk10V3FZSHlMUm12RmlzWk5lRkFKSHlOSExIRm1wTl9Jeko5MU5fSFE3a08wdGVJaWVQbkEtQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>info@p1fo.com</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>https://p1fo.com</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
         <is>
           <t>inference</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>Wed, 20 May 2026</t>
-        </is>
-      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>8183973514</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0002102280</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dalio Family Office</t>
+          <t>Korys</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>press names one individual behind the office ('Ray Dalio') [https://news.google.com/rss/articles/CBMiswFBVV95cUxOY0I1LWVqN0NDcEZ4NjdjMGtmZV9PX0pnNzBVWE54TW1vSXJDd1JXMTk5X0c5bEZiUHlqaGZqaV9lRVRIdTc4RjBBeWhTQlZBM1JSV1Fkb1VHSkcwLUFRZTFXVkJFV3hBY2ZIenhmdXFhTkQ1RWtzellvVkNRbUJuZUpEcGtOTDRTZmQ4Z1piWEhIaFRBeGt2NDV3ZG8zdHJRc0xxdUJsVWFDajFESkVCVk5rVQ?oc=5] (inference/medium)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.korys.be</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/korys</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Tue, 07 Apr 2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J17" t="n">
         <v>35</v>
       </c>
@@ -3919,11 +4039,31 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>We focus on 3 investment themes. Korys creates a thriving ecosystem across these themes, in which the companies involved complement and reinforce each other, consistently increasing the joint impact.</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>https://www.korys.be</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
@@ -3931,42 +4071,38 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Korys · Investing is our commitment to the future Our approach Our portfolio Our insights Our culture Our team Sustainability Investing is our commitment to the future Korys is the entrepreneurial investment company of the Colruyt family. To shape the world we want for ourselves and future generations: that’s what drives us. We work together with other companies toward this shared goal, investing</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>https://www.korys.be</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Ray Dalio</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOY0I1LWVqN0NDcEZ4NjdjMGtmZV9PX0pnNzBVWE54TW1vSXJDd1JXMTk5X0c5bEZiUHlqaGZqaV9lRVRIdTc4RjBBeWhTQlZBM1JSV1Fkb1VHSkcwLUFRZTFXVkJFV3hBY2ZIenhmdXFhTkQ1RWtzellvVkNRbUJuZUpEcGtOTDRTZmQ4Z1piWEhIaFRBeGt2NDV3ZG8zdHJRc0xxdUJsVWFDajFESkVCVk5rVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>named in news headline (unverified)</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Fri, 20 Feb 2026</t>
-        </is>
-      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
@@ -3993,17 +4129,17 @@
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>CIO Mark Baumgartner Departs Dalio Family Office After Less Than a Year - Institutional Investor</t>
+          <t>Euro Company advances sustainability strategy and Korys partnership - FreshPlaza</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNaFNOVzdiVE1pLW10QlYwZVV5ZEJNRkFialJFV0JOOVJUQmZCamtJSEN5T3VTMUxLR1NENzNjeXlOeTRxX2FRQzR4V0NIMjNoVU14U0hEcTdSXzNfVTRxdW5QUHRuTE9SNHVNcVhyTjc4cVpjN2hfMlRkU191V2htVDI0VFp6MlR6TnhBZDRhN2xsaFdUNFNEb0pvNTdSZXhnNGZSb01fdzAySEFmcER4VUtvcG4teXZGVEM1STRhbUFFQzd6clMtc3RpRzRJZnBjWGEtMExNWERWZU5CR3pPT0k1dEk4c2dK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQMnloWlg3a0tfTjlwSmxJSlljMHlZc0xMYmQwc2tQejkxNU9nZUFiZ2JTR2pQVExoWXpMdmo1V2dVS05SOEtlR1lrMUJpRWRDS1lfRS0wWmMtSm56dVA4XzQteW02WmpIWVFzckxMeU1SVHZyVzFlZXc2eGdDRl9uN3F6d3JsNE5IOWdfN2hiRGI3TlZfRjFnUE5TcHN3U0tJUHlUQ1pIYVg2cDc2Y1NzeThDNExCS2dWQmc?oc=5</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>news headline</t>
+          <t>targeted news query</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -4018,36 +4154,56 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>Thu, 15 Aug 2024</t>
+          <t>Tue, 07 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sunil Singhanias Family Office</t>
+          <t>Builders Vision</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>press names one individual behind the office ('Investor Sunil Singhania') [https://news.google.com/rss/articles/CBMikwJBVV95cUxPeHl1SDNEUmwzdXpNVERpc2J2ZUY5elNTc29YdEFCSVAxMHZQRDZGOU1vOGpDUml2ZVV6a3g5dWQtR3lWYnlxR3VvNUhBNEtweUI4c3kwd3RQcXJUa2dfV1lEZ211Yldxb0hzamptNTctYVNMQUptWVJnZVZKLWNNZ1pDOXdHNURwdDhOVHE5bGctTWl1Si04bFpSRXR5X3R2dm9ubjJMRVJpOFloSXNaeHRwVFg0STBjSlVXSlhpeEszMi1zYjBCRWpQenJGdEtrTzJscmxuNVNfYldhdC1sRkV6NWpreS1xR3hjN1RDZFNpZW0xZW1OSEl2ekRGNWowVFMxbTVCOG1iLWh4V3RaTzU5WdIBmAJBVV95cUxPRGQ4Z09RMGxTTmJ2enRNczFUVDdGdG9nYmI5SlloemdvRXJFdHdKblBJc2dDZDZ1bXdhQ3N2bUx1NldMeUh2SzhhaWpiRk51Vkw1MVhEWGR5Zmp6RDVGdzFNOWtSVmdCV0VwVm1rU2hjbGJmYkhRdGJnR0FkWlp5ejdGbWxLb0RwUGNfN3RNTVdHdXZEVkV2dnpKenZGMlR1V3R3M21FX21MV0lXdzlxLTBSMzhGQWtnWnQzdUpVYTg1bmhiUUQ2V21hazRjQWwzbDNMQW1zWFJhWU5TYlBIUXluVWpaOTRXdEd2N0IyMWRKV05yYTUzU1ZoN0sxZXFoRlN0RkFkaUp6RTZ1bzdKOXhLdW94a0Fh?oc=5] (inference/medium)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/builders-vision</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J18" t="n">
         <v>35</v>
       </c>
@@ -4063,11 +4219,31 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>As detailed in the Financial Times: "Walton’s theory of change requires going one step further than picking individual investments: it requires a ‘systems approach’ that pulls in reform-minded organisations in an effort to collectively shift given sectors onto a more impact-friendly footing."</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -4075,42 +4251,38 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>We grow and transform markets that generate financial returns and drive sustainable outcomes.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Investor Sunil Singhania</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPeHl1SDNEUmwzdXpNVERpc2J2ZUY5elNTc29YdEFCSVAxMHZQRDZGOU1vOGpDUml2ZVV6a3g5dWQtR3lWYnlxR3VvNUhBNEtweUI4c3kwd3RQcXJUa2dfV1lEZ211Yldxb0hzamptNTctYVNMQUptWVJnZVZKLWNNZ1pDOXdHNURwdDhOVHE5bGctTWl1Si04bFpSRXR5X3R2dm9ubjJMRVJpOFloSXNaeHRwVFg0STBjSlVXSlhpeEszMi1zYjBCRWpQenJGdEtrTzJscmxuNVNfYldhdC1sRkV6NWpreS1xR3hjN1RDZFNpZW0xZW1OSEl2ekRGNWowVFMxbTVCOG1iLWh4V3RaTzU5WdIBmAJBVV95cUxPRGQ4Z09RMGxTTmJ2enRNczFUVDdGdG9nYmI5SlloemdvRXJFdHdKblBJc2dDZDZ1bXdhQ3N2bUx1NldMeUh2SzhhaWpiRk51Vkw1MVhEWGR5Zmp6RDVGdzFNOWtSVmdCV0VwVm1rU2hjbGJmYkhRdGJnR0FkWlp5ejdGbWxLb0RwUGNfN3RNTVdHdXZEVkV2dnpKenZGMlR1V3R3M21FX21MV0lXdzlxLTBSMzhGQWtnWnQzdUpVYTg1bmhiUUQ2V21hazRjQWwzbDNMQW1zWFJhWU5TYlBIUXluVWpaOTRXdEd2N0IyMWRKV05yYTUzU1ZoN0sxZXFoRlN0RkFkaUp6RTZ1bzdKOXhLdW94a0Fh?oc=5</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>named in news headline (unverified)</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Fri, 31 Oct 2025</t>
-        </is>
-      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="inlineStr"/>
@@ -4137,17 +4309,17 @@
       <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>Ace Investor Sunil Singhanias Family Office Backs SPC (Swapnil Patnis Classes) Indias Leading CA Coaching Brand Enters Pre-IPO Growth Phase - The Tribune</t>
+          <t>Builders Vision adds innovation director to advance food, energy &amp; oceans strategy - Markets Group</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPS0ZBemFJcXRSV1c2Q3prcklxemx4U25ZRTBRdGRLUUJmWWFnTmthaVJUSllucFJ6NGxLZFY2MUVRbzN2TkhWcWpEd0J2RFBVc2lJSzBhUUpxOWtSZEtESHlsRkM2dEhsU2s0N0c2LWlLbEVCSU51LTZGZnNkSjRDSzRTNVg0bVEyOXNEWXFkZWpaa0h0SzVpVVhsa3UySTIyS05kZW1yOW5KMUFpenNzVHdKOWVVY2gta185U3Q1dE1Wc3pxWFA1OXJIRVgtNklKZmUzUmdfc0ZINmdPLWtLWHFJam9TRXlhOHRmNUN0WXNKQXEycVRqa3kteU94b3YwS1NWU0FZRU9MRjhXcmfSAZICQVVfeXFMTi15d2lYWjhaZWhiZ05udFlWR2x3cGIwNmtqeFVza1BkcXNCcVBJdXJfRS14NmF1YmI4MDJLVUxfVmZyZUdzMXRyV2JBX3dKbm13amlOdzNQbmtHTWp4YWc3LTZvb0tXcjE2X0Y5Q19jVUFlUnI4ZHdELTNXZTRnZkxlT3M1ZFR6ck5uTkgwd2FfQmI4T1R3dnhhSjBSMjNVTUlEOXA2bmN0TlJxU0JCMnVsMFVndFVTZFc5cXZxOVJ5aVlndlBFUC1tYU5tNDJMbl9feTBYOXhybWlycFN1WHozT054SDJuY25xMEVpS3J1ekpOS0d1T3Q5N2VTeG1kcjBteFM3RFRQNzFRSktnY2Vadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9sSkVacmpuUlhKUzNWdUdnY0xqWnk1THhoaVNGOF85NGhBZXpoU0piWExjdGpzb3B5SjVRd3BLWHJ1SXZENEo3VVZYV3lleFJaVlFFaXcxUmIzUjNzUFNLNzRDV0Z2OUFWcG85NzdhWjlEYmhzWnd3WQ?oc=5</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>news headline</t>
+          <t>targeted news query</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -4162,19 +4334,19 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>Fri, 31 Oct 2025</t>
+          <t>Tue, 14 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Genspring Family Offices Llc</t>
+          <t>FAMILY OFFICE OF AMERICA, INC.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>SEC EDGAR full-text search</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4184,19 +4356,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001318447) with verified filing address/phone; single- vs multi-family split unproven</t>
+          <t>SEC-registered operating entity (CIK 0001871181) with verified filing address/phone; single- vs multi-family split unproven</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>150 SOUTH U.S. HIGHWAY 1, JUPITER, FL, 33477</t>
+          <t>6898 S. UNIVERSITY BLVD.,, SUITE 100, CENTENNIAL, CO, 80122</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wed, 17 Oct 2012</t>
+          <t>Sat, 25 Jul 2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4231,12 +4403,36 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>SEC-registered filer; industry: Surgical &amp; Medical Instruments &amp; Apparatus.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001871181</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>SEC entity record</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
@@ -4263,12 +4459,12 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>561-354-2551</t>
+          <t>303-874-7474</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001318447</t>
+          <t>SEC EDGAR submissions CIK 0001871181</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -4288,17 +4484,17 @@
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>How being a $19-billion family office roll-up owned by a bank finally caught up with GenSpring - RIABiz</t>
+          <t>Enterprise value to revenue forward of Family Office of America Inc. – OTC:FOFA - TradingView</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNS015ZDRPX2tnY3ZMbXJQa0JFbndlai1ZellqYndvR0pRVmQ2YnFxbzRSWGQ1MEg4UTVDNjE2d1U0UnVROHRpYzctMDBEU2J2aFlnSkFlZE11ZllwMzE4bi1DazlHZ1JvdkhoOTBiR2N4RFZlRUFyaE91b1l3M3E4TFJJNnlzVFJYU1NfN05xZ2ZhMWk1S1N2dDdBLWs5UFk0ZmcxWWY4M1hOM2FEYko0d2xTZmstYUhoWFJsckhIVWJFUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQaklaZnEwRDJjU3ppT3VGZmU2cUlHZGpQa2xscGU0aWVCQkRZaWJDdGpJSHpJdGMzLUNZdTZLWmJyRXdxZ1ZPTTlGSmg2MS1BdHBIZDRuZGxvZUJSc1VTc2k1M09VRHRSWDdtMVROR1Vid05kRXNBeU1xaVJmRWptQmxlVlE3NXE5YWdvaHpCcEJkeE85eXY4MUJiRG1Ud1NjV29EUXVvajg?oc=5</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -4318,50 +4514,38 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>Wed, 17 Oct 2012</t>
+          <t>Sat, 25 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Waveland Family Office, Llc</t>
+          <t>AC Family Office</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0002007105) with verified filing address/phone; single- vs multi-family split unproven</t>
+          <t>press names one individual behind the office ('Henry Pizzutello') [https://news.google.com/rss/articles/CBMi6wFBVV95cUxQLW1hX3hlQVlSYnVycDVTbkhyTTRXUjJBTWtkalVZSFpJc29OMVFQeEgzVWRCM3VVTlBCX0prNEtnbXhybEZuaC04Y3AzMFRrYjgteldQRk1adk5rNVJzVUlHVDg0eU9tYm1ZdGRvOTlxRTg3b3AzY292THJLNVlQaGJSMzVmdTIzZDk0TWJEWWN0ZmRFanBqbm1XY0tibmpGTU9zT3J6dGktTTZYYzlpOFd0T2Q5X3F5OG1xMGhZUVVIbUhSRkg5ZERpMXA2VGdKZHZWQldLMXo3NXBFbVZtNFJObzJCdi1ueGtB?oc=5] (inference/medium)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>570 LAKE COOK RD, SUITE 320, DEERFIELD, IL, 60015</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Tue, 04 Feb 2025</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4393,12 +4577,36 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Henry Pizzutello</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQLW1hX3hlQVlSYnVycDVTbkhyTTRXUjJBTWtkalVZSFpJc29OMVFQeEgzVWRCM3VVTlBCX0prNEtnbXhybEZuaC04Y3AzMFRrYjgteldQRk1adk5rNVJzVUlHVDg0eU9tYm1ZdGRvOTlxRTg3b3AzY292THJLNVlQaGJSMzVmdTIzZDk0TWJEWWN0ZmRFanBqbm1XY0tibmpGTU9zT3J6dGktTTZYYzlpOFd0T2Q5X3F5OG1xMGhZUVVIbUhSRkg5ZERpMXA2VGdKZHZWQldLMXo3NXBFbVZtNFJObzJCdi1ueGtB?oc=5</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>named in news headline (unverified)</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026</t>
+        </is>
+      </c>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
@@ -4417,49 +4625,25 @@
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>312-961-7612</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002007105</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
-      </c>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>CLEARSTEAD ADVISORS ANNOUNCES ACQUISITION OF WAVELAND FAMILY OFFICE - PR Newswire</t>
+          <t>AC Family Office Recruits Henry Pizzutello to Expand Presence in The Woodlands and Beaumont Regions - Morningstar</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQX0MtMV9XT1JNRjFfdlpwc3p1MEg4ZTJ4a050ZDFTQ2gzWEVOc25TaVAwaEFOWE02aXdid3g4QjUwN1lYRGt4ajE1aDBVYy1kWHkwMng0WUVVMUVTd2dtNlZFeS15M3F1M09ndmF5RVI0SmUxUmpQdnozQ2tVem1HOTRQaGR4UG1XcVYteTFQSm1xVVlPUnhCRlFxYVFsUE1uRWRocFdITy0xcFpUWVpYYlJFZUxhSV9tT09DczBsUUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPeGpUbkI4NXJYV052dVlvZnlIY0x1cGZJM3Y3ckRyUFk1RExDYWFoVGVjaDd5R1NKWEdZYmFkaGdjZzNxMlRRRGNNSDdSMGg0bGNESUoyUUNNajgzWFFZN0RZR1p5RkgyQlk2ejF6VjRIOE5BcnhHMUtzbTVjcmZNdGpKelFsZkFXaThlZ294c1BjTDVJMVljTmxSYndGOGFQRjVLT3cyRWM2X01xZlpjX3duRHhxY2lBcnJWZk10V3FZSHlMUm12RmlzWk5lRkFKSHlOSExIRm1wTl9Jeko5MU5fSFE3a08wdGVJaWVQbkEtQQ?oc=5</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>targeted news query</t>
+          <t>news headline</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -4474,46 +4658,38 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>Tue, 04 Feb 2025</t>
+          <t>Wed, 20 May 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, Llc</t>
+          <t>Dalio Family Office</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Biltmore Family Office, Llc' (SEC 13F-HR 2026-05-11 (CIK 0001731123)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://biltmorefamilyoffice.com</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>500 EAST BOULEVARD, CHARLOTTE, NC, 28203</t>
-        </is>
-      </c>
+          <t>press names one individual behind the office ('Ray Dalio') [https://news.google.com/rss/articles/CBMiswFBVV95cUxOY0I1LWVqN0NDcEZ4NjdjMGtmZV9PX0pnNzBVWE54TW1vSXJDd1JXMTk5X0c5bEZiUHlqaGZqaV9lRVRIdTc4RjBBeWhTQlZBM1JSV1Fkb1VHSkcwLUFRZTFXVkJFV3hBY2ZIenhmdXFhTkQ1RWtzellvVkNRbUJuZUpEcGtOTDRTZmQ4Z1piWEhIaFRBeGt2NDV3ZG8zdHJRc0xxdUJsVWFDajFESkVCVk5rVQ?oc=5] (inference/medium)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4521,36 +4697,12 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>$715.5M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4571,64 +4723,40 @@
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Christopher H. A. Cecil</t>
+          <t>Ray Dalio</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOY0I1LWVqN0NDcEZ4NjdjMGtmZV9PX0pnNzBVWE54TW1vSXJDd1JXMTk5X0c5bEZiUHlqaGZqaV9lRVRIdTc4RjBBeWhTQlZBM1JSV1Fkb1VHSkcwLUFRZTFXVkJFV3hBY2ZIenhmdXFhTkQ1RWtzellvVkNRbUJuZUpEcGtOTDRTZmQ4Z1piWEhIaFRBeGt2NDV3ZG8zdHJRc0xxdUJsVWFDajFESkVCVk5rVQ?oc=5</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>13F signature block</t>
+          <t>named in news headline (unverified)</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>fact</t>
+          <t>inference</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>President/Chief Compliance Officer</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>Fri, 20 Feb 2026</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
@@ -4641,79 +4769,71 @@
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>704-272-4698</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001731123</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
-      <c r="BQ21" t="inlineStr"/>
-      <c r="BR21" t="inlineStr"/>
-      <c r="BS21" t="inlineStr"/>
-      <c r="BT21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>CIO Mark Baumgartner Departs Dalio Family Office After Less Than a Year - Institutional Investor</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNaFNOVzdiVE1pLW10QlYwZVV5ZEJNRkFialJFV0JOOVJUQmZCamtJSEN5T3VTMUxLR1NENzNjeXlOeTRxX2FRQzR4V0NIMjNoVU14U0hEcTdSXzNfVTRxdW5QUHRuTE9SNHVNcVhyTjc4cVpjN2hfMlRkU191V2htVDI0VFp6MlR6TnhBZDRhN2xsaFdUNFNEb0pvNTdSZXhnNGZSb01fdzAySEFmcER4VUtvcG4teXZGVEM1STRhbUFFQzd6clMtc3RpRzRJZnBjWGEtMExNWERWZU5CR3pPT0k1dEk4c2dK?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>Thu, 15 Aug 2024</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Sunil Singhanias Family Office</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://bosfam.com</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>20 CUSTOM HOUSE STREET, SUITE 700, BOSTON, MA, 02110</t>
-        </is>
-      </c>
+          <t>press names one individual behind the office ('Investor Sunil Singhania') [https://news.google.com/rss/articles/CBMikwJBVV95cUxPeHl1SDNEUmwzdXpNVERpc2J2ZUY5elNTc29YdEFCSVAxMHZQRDZGOU1vOGpDUml2ZVV6a3g5dWQtR3lWYnlxR3VvNUhBNEtweUI4c3kwd3RQcXJUa2dfV1lEZ211Yldxb0hzamptNTctYVNMQUptWVJnZVZKLWNNZ1pDOXdHNURwdDhOVHE5bGctTWl1Si04bFpSRXR5X3R2dm9ubjJMRVJpOFloSXNaeHRwVFg0STBjSlVXSlhpeEszMi1zYjBCRWpQenJGdEtrTzJscmxuNVNfYldhdC1sRkV6NWpreS1xR3hjN1RDZFNpZW0xZW1OSEl2ekRGNWowVFMxbTVCOG1iLWh4V3RaTzU5WdIBmAJBVV95cUxPRGQ4Z09RMGxTTmJ2enRNczFUVDdGdG9nYmI5SlloemdvRXJFdHdKblBJc2dDZDZ1bXdhQ3N2bUx1NldMeUh2SzhhaWpiRk51Vkw1MVhEWGR5Zmp6RDVGdzFNOWtSVmdCV0VwVm1rU2hjbGJmYkhRdGJnR0FkWlp5ejdGbWxLb0RwUGNfN3RNTVdHdXZEVkV2dnpKenZGMlR1V3R3M21FX21MV0lXdzlxLTBSMzhGQWtnWnQzdUpVYTg1bmhiUUQ2V21hazRjQWwzbDNMQW1zWFJhWU5TYlBIUXluVWpaOTRXdEd2N0IyMWRKV05yYTUzU1ZoN0sxZXFoRlN0RkFkaUp6RTZ1bzdKOXhLdW94a0Fh?oc=5] (inference/medium)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4721,36 +4841,12 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>$1.50B (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4771,64 +4867,40 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>George Beal</t>
+          <t>Investor Sunil Singhania</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPeHl1SDNEUmwzdXpNVERpc2J2ZUY5elNTc29YdEFCSVAxMHZQRDZGOU1vOGpDUml2ZVV6a3g5dWQtR3lWYnlxR3VvNUhBNEtweUI4c3kwd3RQcXJUa2dfV1lEZ211Yldxb0hzamptNTctYVNMQUptWVJnZVZKLWNNZ1pDOXdHNURwdDhOVHE5bGctTWl1Si04bFpSRXR5X3R2dm9ubjJMRVJpOFloSXNaeHRwVFg0STBjSlVXSlhpeEszMi1zYjBCRWpQenJGdEtrTzJscmxuNVNfYldhdC1sRkV6NWpreS1xR3hjN1RDZFNpZW0xZW1OSEl2ekRGNWowVFMxbTVCOG1iLWh4V3RaTzU5WdIBmAJBVV95cUxPRGQ4Z09RMGxTTmJ2enRNczFUVDdGdG9nYmI5SlloemdvRXJFdHdKblBJc2dDZDZ1bXdhQ3N2bUx1NldMeUh2SzhhaWpiRk51Vkw1MVhEWGR5Zmp6RDVGdzFNOWtSVmdCV0VwVm1rU2hjbGJmYkhRdGJnR0FkWlp5ejdGbWxLb0RwUGNfN3RNTVdHdXZEVkV2dnpKenZGMlR1V3R3M21FX21MV0lXdzlxLTBSMzhGQWtnWnQzdUpVYTg1bmhiUUQ2V21hazRjQWwzbDNMQW1zWFJhWU5TYlBIUXluVWpaOTRXdEd2N0IyMWRKV05yYTUzU1ZoN0sxZXFoRlN0RkFkaUp6RTZ1bzdKOXhLdW94a0Fh?oc=5</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>13F signature block</t>
+          <t>named in news headline (unverified)</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>fact</t>
+          <t>inference</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>Managing Partner</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+          <t>Fri, 31 Oct 2025</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
@@ -4841,52 +4913,52 @@
       <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>6176240800</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001039807</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr"/>
-      <c r="BP22" t="inlineStr"/>
-      <c r="BQ22" t="inlineStr"/>
-      <c r="BR22" t="inlineStr"/>
-      <c r="BS22" t="inlineStr"/>
-      <c r="BT22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>Ace Investor Sunil Singhanias Family Office Backs SPC (Swapnil Patnis Classes) Indias Leading CA Coaching Brand Enters Pre-IPO Growth Phase - The Tribune</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPS0ZBemFJcXRSV1c2Q3prcklxemx4U25ZRTBRdGRLUUJmWWFnTmthaVJUSllucFJ6NGxLZFY2MUVRbzN2TkhWcWpEd0J2RFBVc2lJSzBhUUpxOWtSZEtESHlsRkM2dEhsU2s0N0c2LWlLbEVCSU51LTZGZnNkSjRDSzRTNVg0bVEyOXNEWXFkZWpaa0h0SzVpVVhsa3UySTIyS05kZW1yOW5KMUFpenNzVHdKOWVVY2gta185U3Q1dE1Wc3pxWFA1OXJIRVgtNklKZmUzUmdfc0ZINmdPLWtLWHFJam9TRXlhOHRmNUN0WXNKQXEycVRqa3kteU94b3YwS1NWU0FZRU9MRjhXcmfSAZICQVVfeXFMTi15d2lYWjhaZWhiZ05udFlWR2x3cGIwNmtqeFVza1BkcXNCcVBJdXJfRS14NmF1YmI4MDJLVUxfVmZyZUdzMXRyV2JBX3dKbm13amlOdzNQbmtHTWp4YWc3LTZvb0tXcjE2X0Y5Q19jVUFlUnI4ZHdELTNXZTRnZkxlT3M1ZFR6ck5uTkgwd2FfQmI4T1R3dnhhSjBSMjNVTUlEOXA2bmN0TlJxU0JCMnVsMFVndFVTZFc5cXZxOVJ5aVlndlBFUC1tYU5tNDJMbl9feTBYOXhybWlycFN1WHozT054SDJuY25xMEVpS3J1ekpOS0d1T3Q5N2VTeG1kcjBteFM3RFRQNzFRSktnY2Vadw?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>Fri, 31 Oct 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Callan Family Office, Llc</t>
+          <t>UBS Family Office</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4896,19 +4968,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Callan Family Office, Llc' (SEC 13F-HR 2026-05-13 (CIK 0001938970)); single- vs multi-family unproven</t>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>201 KING OF PRUSSIA ROAD, SUITE 650, RADNOR, PA, 19087</t>
-        </is>
-      </c>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -4921,41 +4989,37 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>$4.41B (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
@@ -4963,72 +5027,44 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>John Ginter</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>CEO and CCO</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
@@ -5041,52 +5077,52 @@
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>(267) 250-2036</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001938970</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr"/>
-      <c r="BP23" t="inlineStr"/>
-      <c r="BQ23" t="inlineStr"/>
-      <c r="BR23" t="inlineStr"/>
-      <c r="BS23" t="inlineStr"/>
-      <c r="BT23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>UBS Family Office Report Highlights Strong US Exposure, AI Investment - Family Wealth Report</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWUF1RHNZRmdaSm5HanF5d3M5QWNja2NaVmNnN3RMcE85NVZxWnJnTlpTdkU5ODVWWlQxS2s2Qy1Wa1RCZ1NTWmRGRTluUVVreWM1dnpjY2haZnloS2l2YThheUhLNmhHaGxBSk9hSl9XS25fbkR1Y05lblhLY0p3Nmp3T2Q3NDEwYXkyczVITVFacTFsMmdaTXpwbU5vS0N2ZUpMUTByTkFveFpBNUhLVmlhZjlWbm1DNE9vbg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Collective Family Office Llc</t>
+          <t>UBS Global Family Office</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5096,19 +5132,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Collective Family Office Llc' (SEC 13F-HR 2026-07-02 (CIK 0001845066)); single- vs multi-family unproven</t>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://collectivefamilyoffice.com</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>235 ST. CHARLES WAY, STE. 200, YORK, PA, 17402</t>
-        </is>
-      </c>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -5121,41 +5153,37 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>$489.1M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
@@ -5163,72 +5191,44 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>https://www.ubs.com</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Trevor N. Hoffman</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>CCO/COO</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
@@ -5241,52 +5241,52 @@
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
-      <c r="BI24" t="inlineStr">
-        <is>
-          <t>717-893-5055</t>
-        </is>
-      </c>
-      <c r="BJ24" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001845066</t>
-        </is>
-      </c>
-      <c r="BK24" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM24" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN24" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr"/>
-      <c r="BQ24" t="inlineStr"/>
-      <c r="BR24" t="inlineStr"/>
-      <c r="BS24" t="inlineStr"/>
-      <c r="BT24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>UBS Global Family Office Report 2024: balance is back - Funds Society</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdGVESWZUelkteVdzNzZHdlF2QUM1cHFlYUppOTYxSkJoVWp2QklYU1lnOTlWaTdUcm9ncjZKWGpUOEhVS2FUNWI5ZzZocUI3TkU5Y3JjTWJGWHh5T2hkX2l5S2puOU01NndUZzhtX2ttbF9lLXk3cEtsTE5XV1k1WEJmRHd4YV9YS2ZKbjlrLTZQblVMb0RfRkJrakNYNjg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>Thu, 23 May 2024</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colony Family Offices, Llc</t>
+          <t>Kirloskar Family Office</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Google News RSS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5296,19 +5296,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Colony Family Offices, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001633573)); single- vs multi-family unproven</t>
+          <t>described as family office in gathered text; SFO/MFO split unproven</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://colonyfamilyoffices.com</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>4250 CONGRESS STREET, SUITE 175, CHARLOTTE, NC, 28209</t>
-        </is>
-      </c>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -5321,41 +5317,37 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>$455.1M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>For a period of over 135+ years, we at the Kirloskar Group, affectionately referred to as Kirloskar, have focused on the progress of economic self-sufficiency and industrial growth in India. Our first products, the iron plough and chaff cutters, were introduced by our founder Hon. Late Shri Laxmanra</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>site copy (investing language)</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
@@ -5363,72 +5355,44 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Welcome to the official website of Kirloskar, Explore the legacy of Kirloskar Group - Your trusted source for information about Kirloskar Companies with over 135 + years of industrial excellence</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>http://www.kirloskar.com</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Eric D. Ridenour</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>Managing Director/Chief Compliance Officer</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="inlineStr"/>
@@ -5441,47 +5405,47 @@
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>704-285-7300</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0001633573</t>
-        </is>
-      </c>
-      <c r="BK25" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM25" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="BO25" t="inlineStr"/>
-      <c r="BP25" t="inlineStr"/>
-      <c r="BQ25" t="inlineStr"/>
-      <c r="BR25" t="inlineStr"/>
-      <c r="BS25" t="inlineStr"/>
-      <c r="BT25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>Kirloskar Family Office, Madhusudan Kela back Artha Group’s Rs 450 cr micro-VC fund - Business Today</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNVkl5WXV3Q2liTG0tcXRrOW5hNnlMdmQ4WW5TQXZNVVBLZ2VNTVhTV0NnV3FFOHUxYWljQW5lN09zemxEQXdfam5PT1I3cUNQRWZKZE1ycFhZWDRxa1FlV09LWnlBWHFuaTdyVEFQM3NFejlQWVJWaWxjdVp5Q0o5dnhsNmdaNzZtWHVNUEdQQlh5eWRrNGdMQ2RiN1pFVVJteGFMcC1wYlNGSWRZQlo5WThzaUFKT25hdENBbkdHaGNTSmZFVlVQdHlPX0hkV1k5QWxkLVB3elRveVdpRG1Ja2kxMUZ3Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>news headline</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>Tue, 11 Oct 2022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Custos Family Office, Llc</t>
+          <t>Genspring Family Offices Llc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5496,24 +5460,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Custos Family Office, Llc' (SEC 13F-HR 2026-02-17 (CIK 0001904423)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://custosfo.com</t>
-        </is>
-      </c>
+          <t>SEC-registered operating entity (CIK 0001318447) with verified filing address/phone; single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9011 MOUNTAIN RIDGE DRIVE, SUITE 200, AUSTIN, TX, 78759</t>
+          <t>150 SOUTH U.S. HIGHWAY 1, JUPITER, FL, 33477</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Wed, 17 Oct 2012</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5521,36 +5489,12 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>$146.5M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -5569,66 +5513,18 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Mitchell Herr</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
@@ -5643,12 +5539,12 @@
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>3035787024</t>
+          <t>561-354-2551</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001904423</t>
+          <t>SEC EDGAR submissions CIK 0001318447</t>
         </is>
       </c>
       <c r="BK26" t="inlineStr">
@@ -5668,20 +5564,44 @@
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="BO26" t="inlineStr"/>
-      <c r="BP26" t="inlineStr"/>
-      <c r="BQ26" t="inlineStr"/>
-      <c r="BR26" t="inlineStr"/>
-      <c r="BS26" t="inlineStr"/>
-      <c r="BT26" t="inlineStr"/>
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>How being a $19-billion family office roll-up owned by a bank finally caught up with GenSpring - RIABiz</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNS015ZDRPX2tnY3ZMbXJQa0JFbndlai1ZellqYndvR0pRVmQ2YnFxbzRSWGQ1MEg4UTVDNjE2d1U0UnVROHRpYzctMDBEU2J2aFlnSkFlZE11ZllwMzE4bi1DazlHZ1JvdkhoOTBiR2N4RFZlRUFyaE91b1l3M3E4TFJJNnlzVFJYU1NfN05xZ2ZhMWk1S1N2dDdBLWs5UFk0ZmcxWWY4M1hOM2FEYko0d2xTZmstYUhoWFJsckhIVWJFUVk?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>Wed, 17 Oct 2012</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Geller Family Office Services, Llc</t>
+          <t>Waveland Family Office, Llc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5696,24 +5616,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Geller Family Office Services, Llc' (SEC 13F-HR 2025-02-14 (CIK 0001354739)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://gellerco.com</t>
-        </is>
-      </c>
+          <t>SEC-registered operating entity (CIK 0002007105) with verified filing address/phone; single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>909 THIRD AVENUE, 16TH FLOOR, ATTN: CHIEF COMPLIANCE OFFICER, NEW YORK, NY, 10022</t>
+          <t>570 LAKE COOK RD, SUITE 320, DEERFIELD, IL, 60015</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tue, 04 Feb 2025</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -5721,36 +5645,12 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>$1.52B (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -5769,66 +5669,18 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Beverly Duke</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>Chief Compliance Officer</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
@@ -5843,12 +5695,12 @@
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>212-583-6000</t>
+          <t>312-961-7612</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001354739</t>
+          <t>SEC EDGAR submissions CIK 0002007105</t>
         </is>
       </c>
       <c r="BK27" t="inlineStr">
@@ -5868,25 +5720,49 @@
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="BO27" t="inlineStr"/>
-      <c r="BP27" t="inlineStr"/>
-      <c r="BQ27" t="inlineStr"/>
-      <c r="BR27" t="inlineStr"/>
-      <c r="BS27" t="inlineStr"/>
-      <c r="BT27" t="inlineStr"/>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>CLEARSTEAD ADVISORS ANNOUNCES ACQUISITION OF WAVELAND FAMILY OFFICE - PR Newswire</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQX0MtMV9XT1JNRjFfdlpwc3p1MEg4ZTJ4a050ZDFTQ2gzWEVOc25TaVAwaEFOWE02aXdid3g4QjUwN1lYRGt4ajE1aDBVYy1kWHkwMng0WUVVMUVTd2dtNlZFeS15M3F1M09ndmF5RVI0SmUxUmpQdnozQ2tVem1HOTRQaGR4UG1XcVYteTFQSm1xVVlPUnhCRlFxYVFsUE1uRWRocFdITy0xcFpUWVpYYlJFZUxhSV9tT09DczBsUUg?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>Tue, 04 Feb 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Heritage Family Offices, Llp</t>
+          <t>Revisio Family Office</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5896,24 +5772,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Heritage Family Offices, Llp' (SEC 13F-HR 2026-04-08 (CIK 0002019316)); single- vs multi-family unproven</t>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://heritagefo.com</t>
+          <t>https://revisio-family.de</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9841 E BELL RD,, STE 110, SCOTTSDALE, AZ, 85260</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5921,36 +5797,12 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>$225.5M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -5963,114 +5815,86 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Ganzheitliche Betreuung von Familieninteressen, Nachlassverwaltung, Testamentsvollstreckung, Controlling, Compliance, Digitalisierung</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>https://revisio-family.de</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Michael Frost</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>CCO</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
-      <c r="BF28" t="inlineStr"/>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
-      <c r="BI28" t="inlineStr">
-        <is>
-          <t>602-775-5400</t>
-        </is>
-      </c>
-      <c r="BJ28" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002019316</t>
-        </is>
-      </c>
-      <c r="BK28" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM28" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN28" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>info@revisio-family.de</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>https://revisio-family.de</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>MX record present (domain accepts mail)</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
       <c r="BO28" t="inlineStr"/>
       <c r="BP28" t="inlineStr"/>
       <c r="BQ28" t="inlineStr"/>
@@ -6081,7 +5905,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Riverglades Family Offices Llc</t>
+          <t>Biltmore Family Office, Llc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6096,17 +5920,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Biltmore Family Office, Llc' (SEC 13F-HR 2026-05-11 (CIK 0001731123)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://rivergladesfo.com</t>
+          <t>https://biltmorefamilyoffice.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
+          <t>500 EAST BOULEVARD, CHARLOTTE, NC, 28203</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -6123,12 +5947,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>$170.1M (13F portfolio value)</t>
+          <t>$715.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -6148,7 +5972,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -6171,12 +5995,12 @@
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>PJ Marinelli</t>
+          <t>Christopher H. A. Cecil</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -6196,17 +6020,17 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>President/Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1731123/000139834426008905/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -6226,7 +6050,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr"/>
@@ -6243,12 +6067,12 @@
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>2392634079</t>
+          <t>704-272-4698</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001619779</t>
+          <t>SEC EDGAR submissions CIK 0001731123</t>
         </is>
       </c>
       <c r="BK29" t="inlineStr">
@@ -6268,7 +6092,7 @@
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr"/>
@@ -6281,7 +6105,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stokes Family Office, Llc</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6296,17 +6120,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Boston Family Office Llc' (SEC 13F-HR 2026-05-13 (CIK 0001039807)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com</t>
+          <t>https://bosfam.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
+          <t>20 CUSTOM HOUSE STREET, SUITE 700, BOSTON, MA, 02110</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -6323,12 +6147,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>$969.0M (13F portfolio value)</t>
+          <t>$1.50B (13F portfolio value)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -6348,7 +6172,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -6371,12 +6195,12 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Charles Tiblier</t>
+          <t>George Beal</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -6396,17 +6220,17 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>CCO</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -6426,7 +6250,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr"/>
@@ -6443,12 +6267,12 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>5043994100</t>
+          <t>6176240800</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001802278</t>
+          <t>SEC EDGAR submissions CIK 0001039807</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
@@ -6468,7 +6292,7 @@
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr"/>
@@ -6481,7 +6305,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Timonier Family Office, Ltd.</t>
+          <t>Callan Family Office, Llc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6496,17 +6320,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Callan Family Office, Llc' (SEC 13F-HR 2026-05-13 (CIK 0001938970)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://timonier.com</t>
+          <t>https://callanfamilyoffice.com</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
+          <t>201 KING OF PRUSSIA ROAD, SUITE 650, RADNOR, PA, 19087</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -6523,12 +6347,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>$315.1M (13F portfolio value)</t>
+          <t>$4.41B (13F portfolio value)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -6548,7 +6372,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -6571,12 +6395,12 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Janice French</t>
+          <t>John Ginter</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -6596,17 +6420,17 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>Chief Compliance Office</t>
+          <t>CEO and CCO</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -6626,7 +6450,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr"/>
@@ -6643,12 +6467,12 @@
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>3367255010</t>
+          <t>(267) 250-2036</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002038170</t>
+          <t>SEC EDGAR submissions CIK 0001938970</t>
         </is>
       </c>
       <c r="BK31" t="inlineStr">
@@ -6668,7 +6492,7 @@
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr"/>
@@ -6681,7 +6505,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Virtus Family Office Llc</t>
+          <t>Collective Family Office Llc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6696,17 +6520,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Collective Family Office Llc' (SEC 13F-HR 2026-07-02 (CIK 0001845066)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://virtus-fo.com</t>
+          <t>https://collectivefamilyoffice.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
+          <t>235 ST. CHARLES WAY, STE. 200, YORK, PA, 17402</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -6723,12 +6547,12 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>$117.2M (13F portfolio value)</t>
+          <t>$489.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6748,7 +6572,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -6771,12 +6595,12 @@
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Norma Angelica Peralta Morales</t>
+          <t>Trevor N. Hoffman</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -6796,17 +6620,17 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>CCO/COO</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1845066/000184506626000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -6826,7 +6650,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr"/>
@@ -6843,12 +6667,12 @@
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>9157303885</t>
+          <t>717-893-5055</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001913482</t>
+          <t>SEC EDGAR submissions CIK 0001845066</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
@@ -6868,7 +6692,7 @@
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr"/>
@@ -6881,7 +6705,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, Llc</t>
+          <t>Colony Family Offices, Llc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6896,17 +6720,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Colony Family Offices, Llc' (SEC 13F-HR 2026-07-20 (CIK 0001633573)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://wealthgate.de</t>
+          <t>https://colonyfamilyoffices.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
+          <t>4250 CONGRESS STREET, SUITE 175, CHARLOTTE, NC, 28209</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -6923,12 +6747,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>$35.9M (13F portfolio value)</t>
+          <t>$455.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6948,7 +6772,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -6971,12 +6795,12 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Galen Moore</t>
+          <t>Eric D. Ridenour</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -6996,17 +6820,17 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Managing Director/Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1633573/000139834426012330/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -7026,7 +6850,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr"/>
@@ -7043,12 +6867,12 @@
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>303-968-1737</t>
+          <t>704-285-7300</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001835441</t>
+          <t>SEC EDGAR submissions CIK 0001633573</t>
         </is>
       </c>
       <c r="BK33" t="inlineStr">
@@ -7068,7 +6892,7 @@
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr"/>
@@ -7081,12 +6905,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Custos Family Office, Llc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7096,13 +6920,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Custos Family Office, Llc' (SEC 13F-HR 2026-02-17 (CIK 0001904423)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://custosfo.com</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>701 CARLSON PARKWAY, SUITE 1030, MINNETONKA, MN, 55305</t>
+          <t>9011 MOUNTAIN RIDGE DRIVE, SUITE 200, AUSTIN, TX, 78759</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -7119,12 +6947,12 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>$163.2M (13F portfolio value)</t>
+          <t>$146.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -7144,7 +6972,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -7167,12 +6995,12 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>John P. Flakne</t>
+          <t>Mitchell Herr</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -7192,17 +7020,17 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1904423/000190442326000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -7222,7 +7050,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr"/>
@@ -7239,12 +7067,12 @@
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>952-841-0400</t>
+          <t>3035787024</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001683689</t>
+          <t>SEC EDGAR submissions CIK 0001904423</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
@@ -7264,7 +7092,7 @@
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr"/>
@@ -7277,7 +7105,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Allie Family Office Llc</t>
+          <t>Geller Family Office Services, Llc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7292,13 +7120,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Geller Family Office Services, Llc' (SEC 13F-HR 2025-02-14 (CIK 0001354739)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://gellerco.com</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
+          <t>909 THIRD AVENUE, 16TH FLOOR, ATTN: CHIEF COMPLIANCE OFFICER, NEW YORK, NY, 10022</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -7315,12 +7147,12 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>$228.5M (13F portfolio value)</t>
+          <t>$1.52B (13F portfolio value)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -7340,7 +7172,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -7363,12 +7195,12 @@
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Daniel Bejarano</t>
+          <t>Beverly Duke</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -7388,17 +7220,17 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1354739/000117266125001093/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -7418,7 +7250,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr"/>
@@ -7435,12 +7267,12 @@
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>7866357162</t>
+          <t>212-583-6000</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001908612</t>
+          <t>SEC EDGAR submissions CIK 0001354739</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
@@ -7460,7 +7292,7 @@
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr"/>
@@ -7473,7 +7305,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Capitol Family Office, Inc.</t>
+          <t>Heritage Family Offices, Llp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7488,13 +7320,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Heritage Family Offices, Llp' (SEC 13F-HR 2026-04-08 (CIK 0002019316)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://heritagefo.com</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1500 NW BETHANY BLVD., SUITE 200, BEAVERTON, OR, 97006</t>
+          <t>9841 E BELL RD,, STE 110, SCOTTSDALE, AZ, 85260</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -7511,12 +7347,12 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>$84.7M (13F portfolio value)</t>
+          <t>$225.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -7536,7 +7372,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -7559,12 +7395,12 @@
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Erica Nortman</t>
+          <t>Michael Frost</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -7584,7 +7420,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7594,7 +7430,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2019316/000201931626000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -7614,7 +7450,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr"/>
@@ -7631,12 +7467,12 @@
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>503-897-0236</t>
+          <t>602-775-5400</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001863768</t>
+          <t>SEC EDGAR submissions CIK 0002019316</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
@@ -7656,7 +7492,7 @@
       </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr"/>
@@ -7669,7 +7505,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Covenant Multifamily Offices, Llc</t>
+          <t>Riverglades Family Offices Llc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7679,18 +7515,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>Unconfirmed</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>firm's own name states multi-family: 'Covenant Multifamily Offices, Llc'; files SEC 13F-HR as 'Covenant Multifamily Offices, Llc' (SEC 13F-HR 2021-10-21 (CIK 0001599749))</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Riverglades Family Offices Llc' (SEC 13F-HR 2026-05-14 (CIK 0001619779)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://rivergladesfo.com</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18756 STONE OAK PARKWAY, SUITE 102, SAN ANTONIO, TX, 78258</t>
+          <t>2640 GOLDEN GATE PKWY, SUITE 105, NAPLES, FL, 34105</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -7707,12 +7547,12 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>$556.9M (13F portfolio value)</t>
+          <t>$170.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -7732,7 +7572,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -7755,12 +7595,12 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Kristina Craig</t>
+          <t>PJ Marinelli</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -7780,17 +7620,17 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1619779/000161977926000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -7810,7 +7650,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr"/>
@@ -7827,12 +7667,12 @@
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>210-403-5350</t>
+          <t>2392634079</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001599749</t>
+          <t>SEC EDGAR submissions CIK 0001619779</t>
         </is>
       </c>
       <c r="BK37" t="inlineStr">
@@ -7852,7 +7692,7 @@
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr"/>
@@ -7865,7 +7705,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cva Family Office, Llc</t>
+          <t>Stokes Family Office, Llc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7880,13 +7720,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Stokes Family Office, Llc' (SEC 13F-HR 2026-05-12 (CIK 0001802278)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://stokesfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>255 FILLMORE STREET, SUITE 500, DENVER, CO, 80206</t>
+          <t>1100 POYDRAS STREET, SUITE 2775, NEW ORLEANS, LA, 70163</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -7903,12 +7747,12 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>$949.6M (13F portfolio value)</t>
+          <t>$969.0M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -7928,7 +7772,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -7951,12 +7795,12 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Dalyce Tinoco</t>
+          <t>Charles Tiblier</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -7976,17 +7820,17 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>Dir of Wealth Advisory</t>
+          <t>CCO</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1802278/000106299326002504/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -8006,7 +7850,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr"/>
@@ -8023,12 +7867,12 @@
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>3032435611</t>
+          <t>5043994100</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001802084</t>
+          <t>SEC EDGAR submissions CIK 0001802278</t>
         </is>
       </c>
       <c r="BK38" t="inlineStr">
@@ -8048,7 +7892,7 @@
       </c>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr"/>
@@ -8061,7 +7905,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intrepid Family Office Llc</t>
+          <t>Timonier Family Office, Ltd.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8076,13 +7920,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Timonier Family Office, Ltd.' (SEC 13F-HR 2026-02-04 (CIK 0002038170)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://timonier.com</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
+          <t>121 REYNOLDA VILLAGE, SUITE B, WINSTON SALEM, NC, 27106</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -8099,12 +7947,12 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>$123.6M (13F portfolio value)</t>
+          <t>$315.1M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -8124,7 +7972,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -8147,12 +7995,12 @@
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Matt Dino</t>
+          <t>Janice French</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -8172,17 +8020,17 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Compliance Office</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/2038170/000203817026000001/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -8202,7 +8050,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr"/>
@@ -8219,12 +8067,12 @@
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>(203) 862-3372</t>
+          <t>3367255010</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001596197</t>
+          <t>SEC EDGAR submissions CIK 0002038170</t>
         </is>
       </c>
       <c r="BK39" t="inlineStr">
@@ -8244,7 +8092,7 @@
       </c>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr"/>
@@ -8257,7 +8105,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office Llc</t>
+          <t>Virtus Family Office Llc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8272,13 +8120,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Virtus Family Office Llc' (SEC 13F-HR 2026-05-07 (CIK 0001913482)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://virtus-fo.com</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10 WESTPORT ROAD, STE C-201, PO BOX 690, WILTON, CT, 06897</t>
+          <t>500 W. OVERLAND AVE, STE 250-Q, EL PASO, TX, 79901</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -8295,12 +8147,12 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>$64.7M (13F portfolio value)</t>
+          <t>$117.2M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -8320,7 +8172,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -8343,12 +8195,12 @@
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>W. Thomas Wingertzahn</t>
+          <t>Norma Angelica Peralta Morales</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -8368,17 +8220,17 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1913482/000121465926005687/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -8398,7 +8250,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr"/>
@@ -8415,12 +8267,12 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>203-762-6135</t>
+          <t>9157303885</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001889527</t>
+          <t>SEC EDGAR submissions CIK 0001913482</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
@@ -8440,7 +8292,7 @@
       </c>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr"/>
@@ -8453,7 +8305,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marcuard Family Office Ltd</t>
+          <t>Wealthgate Family Office, Llc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8468,17 +8320,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Wealthgate Family Office, Llc' (SEC 13F-HR 2024-11-08 (CIK 0001835441)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://marcuardfamilyoffice.com</t>
+          <t>https://wealthgate.de</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
+          <t>5025 PEARL PARKWAY, BOULDER, CO, 80301</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -8495,12 +8347,12 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>$46.5M (13F portfolio value)</t>
+          <t>$35.9M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -8520,7 +8372,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -8541,20 +8393,44 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Galen Moore</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>Managing Partner &amp;amp; Assistant Vice President</t>
+          <t>Chief Compliance Officer</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1835441/000139834424020268/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -8574,7 +8450,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr"/>
@@ -8591,12 +8467,12 @@
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>41 43 344 60 00</t>
+          <t>303-968-1737</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001538112</t>
+          <t>SEC EDGAR submissions CIK 0001835441</t>
         </is>
       </c>
       <c r="BK41" t="inlineStr">
@@ -8616,7 +8492,7 @@
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>2014-10-16</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr"/>
@@ -8629,12 +8505,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oneascent Family Office, Llc</t>
+          <t>Redwood Holdings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>Wikidata (P31: family office)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8644,18 +8520,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Wikidata classifies this entity as a family office (instance of Q751314 'family office'); single- vs multi-family split unproven</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.redwoodholdings.net</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>25</v>
       </c>
@@ -8665,36 +8553,12 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>$143.2M (13F portfolio value)</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -8707,72 +8571,44 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Redwood Holdings Redwood Holdings Home</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>https://www.redwoodholdings.net</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>site homepage / meta description</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Ashleigh Swayze</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>Counsel</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>13F signature block</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="AV42" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr"/>
@@ -8785,52 +8621,52 @@
       <c r="BF42" t="inlineStr"/>
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
-      <c r="BI42" t="inlineStr">
-        <is>
-          <t>2053139142</t>
-        </is>
-      </c>
-      <c r="BJ42" t="inlineStr">
-        <is>
-          <t>SEC EDGAR submissions CIK 0002055812</t>
-        </is>
-      </c>
-      <c r="BK42" t="inlineStr">
-        <is>
-          <t>official SEC filing (business phone)</t>
-        </is>
-      </c>
-      <c r="BL42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="BM42" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
-      <c r="BN42" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="BO42" t="inlineStr"/>
-      <c r="BP42" t="inlineStr"/>
-      <c r="BQ42" t="inlineStr"/>
-      <c r="BR42" t="inlineStr"/>
-      <c r="BS42" t="inlineStr"/>
-      <c r="BT42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+      <c r="BO42" t="inlineStr">
+        <is>
+          <t>Redwood files “RedwoodRe” trademark for reinsurance underwriting - Coverager</t>
+        </is>
+      </c>
+      <c r="BP42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNUUN1a0NqZ3ZiS0E0Qks4T1Y5UU9Ua1I4V2lHemgzb0kwa0NnaEFUQkt1eTl5dGZqdmluZjNSRDZWdUluUFBybkRiUDBkanRsMVhXWjVEcmNiTEFCQjFjTmdlRUlKQkxkdEVRVjVVcDFKb0g0WUlZSUJyNWhXRE9SZk00VGxYT21pUjM4Z0d3?oc=5</t>
+        </is>
+      </c>
+      <c r="BQ42" t="inlineStr">
+        <is>
+          <t>targeted news query</t>
+        </is>
+      </c>
+      <c r="BR42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="BS42" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="BT42" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Standard Family Office Llc</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SEC CIK registry (entity names)</t>
+          <t>SEC EDGAR full-text search</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8840,13 +8676,13 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Standard Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001809494)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Kopp Family Office, LLC' (SEC 13F-HR 2026-07-09 (CIK 0001683689)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7036 SOUTH SANTA ROSA COURT, SUITE 103, SIOUX FALLS, SD, 57108</t>
+          <t>701 CARLSON PARKWAY, SUITE 1030, MINNETONKA, MN, 55305</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -8863,12 +8699,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>$96.8M (13F portfolio value)</t>
+          <t>$163.2M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -8888,7 +8724,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -8911,12 +8747,12 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Kelsey Olson</t>
+          <t>John P. Flakne</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -8936,17 +8772,17 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>Chief Compliance Officer</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1809494/000180949426000011/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -8966,7 +8802,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr"/>
@@ -8983,12 +8819,12 @@
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>6054967760</t>
+          <t>952-841-0400</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001809494</t>
+          <t>SEC EDGAR submissions CIK 0001683689</t>
         </is>
       </c>
       <c r="BK43" t="inlineStr">
@@ -9008,7 +8844,7 @@
       </c>
       <c r="BN43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="BO43" t="inlineStr"/>
@@ -9021,7 +8857,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Allie Family Office Llc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9036,13 +8872,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Tarbox Family Office, Inc.' (SEC 13F-HR 2026-04-24 (CIK 0001599603)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Allie Family Office Llc' (SEC 13F-HR 2026-05-14 (CIK 0001908612)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>500 NEWPORT CENTER DRIVE SUITE 500, NEWPORT BEACH, CA, 92660</t>
+          <t>1200 BRICKELL AVENUE, SUITE 800, MIAMI, FL, 33131</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -9059,12 +8895,12 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>$615.8M (13F portfolio value)</t>
+          <t>$228.5M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -9084,7 +8920,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -9107,12 +8943,12 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Mary Sigler</t>
+          <t>Daniel Bejarano</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -9132,17 +8968,17 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1599603/000159960326000003/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -9162,7 +8998,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr"/>
@@ -9179,12 +9015,12 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>949-721-2330</t>
+          <t>7866357162</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001599603</t>
+          <t>SEC EDGAR submissions CIK 0001908612</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
@@ -9204,7 +9040,7 @@
       </c>
       <c r="BN44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="BO44" t="inlineStr"/>
@@ -9217,12 +9053,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UBS Family Office</t>
+          <t>Capitol Family Office, Inc.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9232,15 +9068,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Capitol Family Office, Inc.' (SEC 13F-HR 2026-04-15 (CIK 0001863768)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1500 NW BETHANY BLVD., SUITE 200, BEAVERTON, OR, 97006</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -9253,37 +9089,41 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>$84.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
@@ -9291,44 +9131,72 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Erica Nortman</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863768/000186376826000004/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="inlineStr"/>
@@ -9341,70 +9209,70 @@
       <c r="BF45" t="inlineStr"/>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
-      <c r="BI45" t="inlineStr"/>
-      <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="inlineStr"/>
-      <c r="BL45" t="inlineStr"/>
-      <c r="BM45" t="inlineStr"/>
-      <c r="BN45" t="inlineStr"/>
-      <c r="BO45" t="inlineStr">
-        <is>
-          <t>UBS Family Office Report Highlights Strong US Exposure, AI Investment - Family Wealth Report</t>
-        </is>
-      </c>
-      <c r="BP45" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWUF1RHNZRmdaSm5HanF5d3M5QWNja2NaVmNnN3RMcE85NVZxWnJnTlpTdkU5ODVWWlQxS2s2Qy1Wa1RCZ1NTWmRGRTluUVVreWM1dnpjY2haZnloS2l2YThheUhLNmhHaGxBSk9hSl9XS25fbkR1Y05lblhLY0p3Nmp3T2Q3NDEwYXkyczVITVFacTFsMmdaTXpwbU5vS0N2ZUpMUTByTkFveFpBNUhLVmlhZjlWbm1DNE9vbg?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ45" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS45" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT45" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026</t>
-        </is>
-      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>503-897-0236</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001863768</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="BO45" t="inlineStr"/>
+      <c r="BP45" t="inlineStr"/>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr"/>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UBS Global Family Office</t>
+          <t>Covenant Multifamily Offices, Llc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unconfirmed</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>firm's own name states multi-family: 'Covenant Multifamily Offices, Llc'; files SEC 13F-HR as 'Covenant Multifamily Offices, Llc' (SEC 13F-HR 2021-10-21 (CIK 0001599749))</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>18756 STONE OAK PARKWAY, SUITE 102, SAN ANTONIO, TX, 78258</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -9417,37 +9285,41 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Investment Bank Investment Bank Visit overview Investment Bank overview What we offer About us Insights Regulatory directory Conferences Investment Bank overview What we offer About us Insights Regulatory directory Conferences</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>$556.9M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -9455,44 +9327,72 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>UBS is a global firm providing financial services in over 50 markets. Visit our site to find out what we offer in your market.</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>https://www.ubs.com</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
-      <c r="AV46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Kristina Craig</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1599749/000110465921128387/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="inlineStr"/>
@@ -9505,52 +9405,52 @@
       <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
-      <c r="BI46" t="inlineStr"/>
-      <c r="BJ46" t="inlineStr"/>
-      <c r="BK46" t="inlineStr"/>
-      <c r="BL46" t="inlineStr"/>
-      <c r="BM46" t="inlineStr"/>
-      <c r="BN46" t="inlineStr"/>
-      <c r="BO46" t="inlineStr">
-        <is>
-          <t>UBS Global Family Office Report 2024: balance is back - Funds Society</t>
-        </is>
-      </c>
-      <c r="BP46" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdGVESWZUelkteVdzNzZHdlF2QUM1cHFlYUppOTYxSkJoVWp2QklYU1lnOTlWaTdUcm9ncjZKWGpUOEhVS2FUNWI5ZzZocUI3TkU5Y3JjTWJGWHh5T2hkX2l5S2puOU01NndUZzhtX2ttbF9lLXk3cEtsTE5XV1k1WEJmRHd4YV9YS2ZKbjlrLTZQblVMb0RfRkJrakNYNjg?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ46" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR46" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS46" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT46" t="inlineStr">
-        <is>
-          <t>Thu, 23 May 2024</t>
-        </is>
-      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>210-403-5350</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001599749</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN46" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="inlineStr"/>
+      <c r="BR46" t="inlineStr"/>
+      <c r="BS46" t="inlineStr"/>
+      <c r="BT46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kirloskar Family Office</t>
+          <t>Cva Family Office, Llc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Google News RSS</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9560,15 +9460,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>described as family office in gathered text; SFO/MFO split unproven</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>files SEC 13F-HR as 'Cva Family Office, Llc' (SEC 13F-HR 2026-04-29 (CIK 0001802084)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>255 FILLMORE STREET, SUITE 500, DENVER, CO, 80206</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -9581,37 +9481,41 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>For a period of over 135+ years, we at the Kirloskar Group, affectionately referred to as Kirloskar, have focused on the progress of economic self-sufficiency and industrial growth in India. Our first products, the iron plough and chaff cutters, were introduced by our founder Hon. Late Shri Laxmanra</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>site copy (investing language)</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>$949.6M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
@@ -9619,44 +9523,72 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>Welcome to the official website of Kirloskar, Explore the legacy of Kirloskar Group - Your trusted source for information about Kirloskar Companies with over 135 + years of industrial excellence</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>http://www.kirloskar.com</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>site homepage / meta description</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>fact</t>
-        </is>
-      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Dalyce Tinoco</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>Dir of Wealth Advisory</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1802084/000180208426000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="inlineStr"/>
@@ -9669,47 +9601,47 @@
       <c r="BF47" t="inlineStr"/>
       <c r="BG47" t="inlineStr"/>
       <c r="BH47" t="inlineStr"/>
-      <c r="BI47" t="inlineStr"/>
-      <c r="BJ47" t="inlineStr"/>
-      <c r="BK47" t="inlineStr"/>
-      <c r="BL47" t="inlineStr"/>
-      <c r="BM47" t="inlineStr"/>
-      <c r="BN47" t="inlineStr"/>
-      <c r="BO47" t="inlineStr">
-        <is>
-          <t>Kirloskar Family Office, Madhusudan Kela back Artha Group’s Rs 450 cr micro-VC fund - Business Today</t>
-        </is>
-      </c>
-      <c r="BP47" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNVkl5WXV3Q2liTG0tcXRrOW5hNnlMdmQ4WW5TQXZNVVBLZ2VNTVhTV0NnV3FFOHUxYWljQW5lN09zemxEQXdfam5PT1I3cUNQRWZKZE1ycFhZWDRxa1FlV09LWnlBWHFuaTdyVEFQM3NFejlQWVJWaWxjdVp5Q0o5dnhsNmdaNzZtWHVNUEdQQlh5eWRrNGdMQ2RiN1pFVVJteGFMcC1wYlNGSWRZQlo5WThzaUFKT25hdENBbkdHaGNTSmZFVlVQdHlPX0hkV1k5QWxkLVB3elRveVdpRG1Ja2kxMUZ3Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="BQ47" t="inlineStr">
-        <is>
-          <t>news headline</t>
-        </is>
-      </c>
-      <c r="BR47" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="BS47" t="inlineStr">
-        <is>
-          <t>inference</t>
-        </is>
-      </c>
-      <c r="BT47" t="inlineStr">
-        <is>
-          <t>Tue, 11 Oct 2022</t>
-        </is>
-      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>3032435611</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>SEC EDGAR submissions CIK 0001802084</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>official SEC filing (business phone)</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="BM47" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="BN47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr"/>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, Llc</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9724,13 +9656,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>files SEC 13F-HR as 'Pioneer Family Office, Llc' (SEC 13F-HR 2026-05-14 (CIK 0002135110)); single- vs multi-family unproven</t>
+          <t>files SEC 13F-HR as 'Intrepid Family Office Llc' (SEC 13F-HR 2026-05-15 (CIK 0001596197)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3323 NE 163RD STREET, SUITE 604, NORTH MIAMI BEACH, FL, 33160</t>
+          <t>2170 MAIN ST, UNIT 404, SARASOTA, FL, 34237</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -9747,12 +9679,12 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>$155.7M (13F portfolio value)</t>
+          <t>$123.6M (13F portfolio value)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -9772,7 +9704,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -9793,20 +9725,44 @@
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Matt Dino</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>COUNSEL</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/2135110/000213511026000002/primary_doc.xml</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -9826,7 +9782,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr"/>
@@ -9843,12 +9799,12 @@
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>305-935-5502</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0002135110</t>
+          <t>SEC EDGAR submissions CIK 0001596197</t>
         </is>
       </c>
       <c r="BK48" t="inlineStr">
@@ -9868,7 +9824,7 @@
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr"/>
@@ -9881,12 +9837,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Longboat Family Office LP</t>
+          <t>Louis-Dreyfus Family Office Llc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9896,17 +9852,13 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001878856) with verified filing address/phone; single- vs multi-family split unproven</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://longboatfamilyoffice.com</t>
-        </is>
-      </c>
+          <t>files SEC 13F-HR as 'Louis-Dreyfus Family Office Llc' (SEC 13F-HR 2022-11-10 (CIK 0001889527)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>500 MAMARONECK AVENUE, SUITE 213, HARRISON, NY, 10528</t>
+          <t>10 WESTPORT ROAD, STE C-201, PO BOX 690, WILTON, CT, 06897</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -9921,12 +9873,36 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>$64.7M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -9945,18 +9921,66 @@
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
-      <c r="AV49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>W. Thomas Wingertzahn</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>2022-11-10</t>
+        </is>
+      </c>
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr"/>
       <c r="AY49" t="inlineStr"/>
@@ -9971,12 +9995,12 @@
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>212-798-1362</t>
+          <t>203-762-6135</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001878856</t>
+          <t>SEC EDGAR submissions CIK 0001889527</t>
         </is>
       </c>
       <c r="BK49" t="inlineStr">
@@ -9996,7 +10020,7 @@
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr"/>
@@ -10009,12 +10033,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pinnacle Family Office Investments L.P.</t>
+          <t>Marcuard Family Office Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SEC EDGAR full-text search</t>
+          <t>SEC CIK registry (entity names)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10024,17 +10048,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001542604) with verified filing address/phone; single- vs multi-family split unproven</t>
+          <t>files SEC 13F-HR as 'Marcuard Family Office Ltd' (SEC 13F-HR 2014-10-16 (CIK 0001538112)); single- vs multi-family unproven</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://pinnacleinvestment.com</t>
+          <t>https://marcuardfamilyoffice.com</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5910 NORTH CENTRAL EXPRESSWAY, SUITE 1475, DALLAS, TX, 75206</t>
+          <t>THEATERSTRASSE 12, ZURICH, V8, 8024</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -10049,12 +10073,36 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>$46.5M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -10079,12 +10127,36 @@
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>Managing Partner &amp;amp; Assistant Vice President</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1538112/000114420414061442/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>2014-10-16</t>
+        </is>
+      </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr"/>
       <c r="AY50" t="inlineStr"/>
@@ -10099,12 +10171,12 @@
       <c r="BH50" t="inlineStr"/>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>469-941-4146</t>
+          <t>41 43 344 60 00</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001542604</t>
+          <t>SEC EDGAR submissions CIK 0001538112</t>
         </is>
       </c>
       <c r="BK50" t="inlineStr">
@@ -10124,7 +10196,7 @@
       </c>
       <c r="BN50" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2014-10-16</t>
         </is>
       </c>
       <c r="BO50" t="inlineStr"/>
@@ -10137,7 +10209,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Antilles Family Office, Llc</t>
+          <t>Oneascent Family Office, Llc</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10152,17 +10224,13 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SEC-registered operating entity (CIK 0001930338) with verified filing address/phone; single- vs multi-family split unproven</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://antillesfamilyoffice.com</t>
-        </is>
-      </c>
+          <t>files SEC 13F-HR as 'Oneascent Family Office, Llc' (SEC 13F-HR 2026-04-21 (CIK 0002055812)); single- vs multi-family unproven</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5330 YACHT HAVEN GRANDE, SUITE 206, ST THOMAS, VI, 00802</t>
+          <t>23 INVERNESS CENTER PARKWAY, BIRMINGHAM, AL, 35242</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -10177,12 +10245,36 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>$143.2M (13F portfolio value)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>13F tableValueTotal — US-listed equities only, not full AUM</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -10201,18 +10293,66 @@
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Ashleigh Swayze</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>Counsel</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2055812/000205581226000002/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>13F signature block</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>fact</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr"/>
       <c r="AY51" t="inlineStr"/>
@@ -10227,12 +10367,12 @@
       <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>3407748800</t>
+          <t>2053139142</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions CIK 0001930338</t>
+          <t>SEC EDGAR submissions CIK 0002055812</t>
         </is>
       </c>
       <c r="BK51" t="inlineStr">
@@ -10252,7 +10392,7 @@
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr"/>
